--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q957"/>
+  <dimension ref="A1:Q958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52466,6 +52466,61 @@
         <v>13322</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>28346</v>
+      </c>
+      <c r="C958" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D958" t="n">
+        <v>3974</v>
+      </c>
+      <c r="E958" t="n">
+        <v>7926</v>
+      </c>
+      <c r="F958" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G958" t="n">
+        <v>14359</v>
+      </c>
+      <c r="H958" t="n">
+        <v>16845</v>
+      </c>
+      <c r="I958" t="n">
+        <v>18707</v>
+      </c>
+      <c r="J958" t="n">
+        <v>20258</v>
+      </c>
+      <c r="K958" t="n">
+        <v>2998</v>
+      </c>
+      <c r="L958" t="n">
+        <v>897</v>
+      </c>
+      <c r="M958" t="n">
+        <v>2257</v>
+      </c>
+      <c r="N958" t="n">
+        <v>353</v>
+      </c>
+      <c r="O958" t="n">
+        <v>3237</v>
+      </c>
+      <c r="P958" t="n">
+        <v>7598</v>
+      </c>
+      <c r="Q958" t="n">
+        <v>13339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52477,7 +52532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B957"/>
+  <dimension ref="A1:B958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62052,6 +62107,16 @@
         <v>11743</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>11783</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q958"/>
+  <dimension ref="A1:Q959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52521,6 +52521,61 @@
         <v>13339</v>
       </c>
     </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>28345</v>
+      </c>
+      <c r="C959" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D959" t="n">
+        <v>3974</v>
+      </c>
+      <c r="E959" t="n">
+        <v>7921</v>
+      </c>
+      <c r="F959" t="n">
+        <v>11466</v>
+      </c>
+      <c r="G959" t="n">
+        <v>14356</v>
+      </c>
+      <c r="H959" t="n">
+        <v>16843</v>
+      </c>
+      <c r="I959" t="n">
+        <v>18698</v>
+      </c>
+      <c r="J959" t="n">
+        <v>20250</v>
+      </c>
+      <c r="K959" t="n">
+        <v>2998</v>
+      </c>
+      <c r="L959" t="n">
+        <v>902</v>
+      </c>
+      <c r="M959" t="n">
+        <v>2257</v>
+      </c>
+      <c r="N959" t="n">
+        <v>352</v>
+      </c>
+      <c r="O959" t="n">
+        <v>3239</v>
+      </c>
+      <c r="P959" t="n">
+        <v>7599</v>
+      </c>
+      <c r="Q959" t="n">
+        <v>13351</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52532,7 +52587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B958"/>
+  <dimension ref="A1:B959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62117,6 +62172,16 @@
         <v>11783</v>
       </c>
     </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>11811</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q959"/>
+  <dimension ref="A1:Q960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52576,6 +52576,61 @@
         <v>13351</v>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>28348</v>
+      </c>
+      <c r="C960" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D960" t="n">
+        <v>3972</v>
+      </c>
+      <c r="E960" t="n">
+        <v>7925</v>
+      </c>
+      <c r="F960" t="n">
+        <v>11469</v>
+      </c>
+      <c r="G960" t="n">
+        <v>14351</v>
+      </c>
+      <c r="H960" t="n">
+        <v>16844</v>
+      </c>
+      <c r="I960" t="n">
+        <v>18698</v>
+      </c>
+      <c r="J960" t="n">
+        <v>20249</v>
+      </c>
+      <c r="K960" t="n">
+        <v>2995</v>
+      </c>
+      <c r="L960" t="n">
+        <v>908</v>
+      </c>
+      <c r="M960" t="n">
+        <v>2261</v>
+      </c>
+      <c r="N960" t="n">
+        <v>349</v>
+      </c>
+      <c r="O960" t="n">
+        <v>3236</v>
+      </c>
+      <c r="P960" t="n">
+        <v>7603</v>
+      </c>
+      <c r="Q960" t="n">
+        <v>13350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52587,7 +52642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B959"/>
+  <dimension ref="A1:B960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62182,6 +62237,16 @@
         <v>11811</v>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>11817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q960"/>
+  <dimension ref="A1:Q961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52631,6 +52631,61 @@
         <v>13350</v>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>28315</v>
+      </c>
+      <c r="C961" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D961" t="n">
+        <v>3965</v>
+      </c>
+      <c r="E961" t="n">
+        <v>7918</v>
+      </c>
+      <c r="F961" t="n">
+        <v>11456</v>
+      </c>
+      <c r="G961" t="n">
+        <v>14335</v>
+      </c>
+      <c r="H961" t="n">
+        <v>16822</v>
+      </c>
+      <c r="I961" t="n">
+        <v>18682</v>
+      </c>
+      <c r="J961" t="n">
+        <v>20243</v>
+      </c>
+      <c r="K961" t="n">
+        <v>2984</v>
+      </c>
+      <c r="L961" t="n">
+        <v>906</v>
+      </c>
+      <c r="M961" t="n">
+        <v>2251</v>
+      </c>
+      <c r="N961" t="n">
+        <v>349</v>
+      </c>
+      <c r="O961" t="n">
+        <v>3237</v>
+      </c>
+      <c r="P961" t="n">
+        <v>7595</v>
+      </c>
+      <c r="Q961" t="n">
+        <v>13337</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52642,7 +52697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B960"/>
+  <dimension ref="A1:B961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62247,6 +62302,16 @@
         <v>11817</v>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>11808</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q961"/>
+  <dimension ref="A1:Q962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52686,6 +52686,61 @@
         <v>13337</v>
       </c>
     </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>28311</v>
+      </c>
+      <c r="C962" t="n">
+        <v>1067</v>
+      </c>
+      <c r="D962" t="n">
+        <v>3961</v>
+      </c>
+      <c r="E962" t="n">
+        <v>7922</v>
+      </c>
+      <c r="F962" t="n">
+        <v>11450</v>
+      </c>
+      <c r="G962" t="n">
+        <v>14336</v>
+      </c>
+      <c r="H962" t="n">
+        <v>16825</v>
+      </c>
+      <c r="I962" t="n">
+        <v>18692</v>
+      </c>
+      <c r="J962" t="n">
+        <v>20250</v>
+      </c>
+      <c r="K962" t="n">
+        <v>2975</v>
+      </c>
+      <c r="L962" t="n">
+        <v>899</v>
+      </c>
+      <c r="M962" t="n">
+        <v>2255</v>
+      </c>
+      <c r="N962" t="n">
+        <v>347</v>
+      </c>
+      <c r="O962" t="n">
+        <v>3241</v>
+      </c>
+      <c r="P962" t="n">
+        <v>7607</v>
+      </c>
+      <c r="Q962" t="n">
+        <v>13354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52697,7 +52752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B961"/>
+  <dimension ref="A1:B962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62312,6 +62367,16 @@
         <v>11808</v>
       </c>
     </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>11834</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q962"/>
+  <dimension ref="A1:Q963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52741,6 +52741,61 @@
         <v>13354</v>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>28313</v>
+      </c>
+      <c r="C963" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D963" t="n">
+        <v>3963</v>
+      </c>
+      <c r="E963" t="n">
+        <v>7923</v>
+      </c>
+      <c r="F963" t="n">
+        <v>11452</v>
+      </c>
+      <c r="G963" t="n">
+        <v>14341</v>
+      </c>
+      <c r="H963" t="n">
+        <v>16835</v>
+      </c>
+      <c r="I963" t="n">
+        <v>18702</v>
+      </c>
+      <c r="J963" t="n">
+        <v>20253</v>
+      </c>
+      <c r="K963" t="n">
+        <v>2972</v>
+      </c>
+      <c r="L963" t="n">
+        <v>898</v>
+      </c>
+      <c r="M963" t="n">
+        <v>2256</v>
+      </c>
+      <c r="N963" t="n">
+        <v>347</v>
+      </c>
+      <c r="O963" t="n">
+        <v>3244</v>
+      </c>
+      <c r="P963" t="n">
+        <v>7613</v>
+      </c>
+      <c r="Q963" t="n">
+        <v>13357</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52752,7 +52807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B962"/>
+  <dimension ref="A1:B963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62377,6 +62432,16 @@
         <v>11834</v>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>11796</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q963"/>
+  <dimension ref="A1:Q964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52796,6 +52796,61 @@
         <v>13357</v>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>28288</v>
+      </c>
+      <c r="C964" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D964" t="n">
+        <v>3965</v>
+      </c>
+      <c r="E964" t="n">
+        <v>7921</v>
+      </c>
+      <c r="F964" t="n">
+        <v>11457</v>
+      </c>
+      <c r="G964" t="n">
+        <v>14328</v>
+      </c>
+      <c r="H964" t="n">
+        <v>16815</v>
+      </c>
+      <c r="I964" t="n">
+        <v>18684</v>
+      </c>
+      <c r="J964" t="n">
+        <v>20242</v>
+      </c>
+      <c r="K964" t="n">
+        <v>2966</v>
+      </c>
+      <c r="L964" t="n">
+        <v>888</v>
+      </c>
+      <c r="M964" t="n">
+        <v>2254</v>
+      </c>
+      <c r="N964" t="n">
+        <v>346</v>
+      </c>
+      <c r="O964" t="n">
+        <v>3243</v>
+      </c>
+      <c r="P964" t="n">
+        <v>7618</v>
+      </c>
+      <c r="Q964" t="n">
+        <v>13349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52807,7 +52862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B963"/>
+  <dimension ref="A1:B964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62442,6 +62497,16 @@
         <v>11796</v>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>11785</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q964"/>
+  <dimension ref="A1:Q965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52851,6 +52851,61 @@
         <v>13349</v>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>28279</v>
+      </c>
+      <c r="C965" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D965" t="n">
+        <v>3953</v>
+      </c>
+      <c r="E965" t="n">
+        <v>7903</v>
+      </c>
+      <c r="F965" t="n">
+        <v>11445</v>
+      </c>
+      <c r="G965" t="n">
+        <v>14323</v>
+      </c>
+      <c r="H965" t="n">
+        <v>16816</v>
+      </c>
+      <c r="I965" t="n">
+        <v>18687</v>
+      </c>
+      <c r="J965" t="n">
+        <v>20248</v>
+      </c>
+      <c r="K965" t="n">
+        <v>2966</v>
+      </c>
+      <c r="L965" t="n">
+        <v>885</v>
+      </c>
+      <c r="M965" t="n">
+        <v>2246</v>
+      </c>
+      <c r="N965" t="n">
+        <v>346</v>
+      </c>
+      <c r="O965" t="n">
+        <v>3235</v>
+      </c>
+      <c r="P965" t="n">
+        <v>7600</v>
+      </c>
+      <c r="Q965" t="n">
+        <v>13342</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52862,7 +52917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B964"/>
+  <dimension ref="A1:B965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62507,6 +62562,16 @@
         <v>11785</v>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>11792</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q965"/>
+  <dimension ref="A1:Q966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52906,6 +52906,61 @@
         <v>13342</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>28276</v>
+      </c>
+      <c r="C966" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D966" t="n">
+        <v>3957</v>
+      </c>
+      <c r="E966" t="n">
+        <v>7888</v>
+      </c>
+      <c r="F966" t="n">
+        <v>11434</v>
+      </c>
+      <c r="G966" t="n">
+        <v>14323</v>
+      </c>
+      <c r="H966" t="n">
+        <v>16819</v>
+      </c>
+      <c r="I966" t="n">
+        <v>18695</v>
+      </c>
+      <c r="J966" t="n">
+        <v>20243</v>
+      </c>
+      <c r="K966" t="n">
+        <v>2959</v>
+      </c>
+      <c r="L966" t="n">
+        <v>890</v>
+      </c>
+      <c r="M966" t="n">
+        <v>2246</v>
+      </c>
+      <c r="N966" t="n">
+        <v>346</v>
+      </c>
+      <c r="O966" t="n">
+        <v>3236</v>
+      </c>
+      <c r="P966" t="n">
+        <v>7593</v>
+      </c>
+      <c r="Q966" t="n">
+        <v>13339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52917,7 +52972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B965"/>
+  <dimension ref="A1:B966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62572,6 +62627,16 @@
         <v>11792</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>11784</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q966"/>
+  <dimension ref="A1:Q967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52961,6 +52961,61 @@
         <v>13339</v>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>28282</v>
+      </c>
+      <c r="C967" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D967" t="n">
+        <v>3943</v>
+      </c>
+      <c r="E967" t="n">
+        <v>7887</v>
+      </c>
+      <c r="F967" t="n">
+        <v>11421</v>
+      </c>
+      <c r="G967" t="n">
+        <v>14311</v>
+      </c>
+      <c r="H967" t="n">
+        <v>16811</v>
+      </c>
+      <c r="I967" t="n">
+        <v>18690</v>
+      </c>
+      <c r="J967" t="n">
+        <v>20238</v>
+      </c>
+      <c r="K967" t="n">
+        <v>2968</v>
+      </c>
+      <c r="L967" t="n">
+        <v>892</v>
+      </c>
+      <c r="M967" t="n">
+        <v>2249</v>
+      </c>
+      <c r="N967" t="n">
+        <v>347</v>
+      </c>
+      <c r="O967" t="n">
+        <v>3232</v>
+      </c>
+      <c r="P967" t="n">
+        <v>7587</v>
+      </c>
+      <c r="Q967" t="n">
+        <v>13343</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52972,7 +53027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B966"/>
+  <dimension ref="A1:B967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62637,6 +62692,16 @@
         <v>11784</v>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>11802</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q967"/>
+  <dimension ref="A1:Q968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53016,6 +53016,61 @@
         <v>13343</v>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>28264</v>
+      </c>
+      <c r="C968" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D968" t="n">
+        <v>3944</v>
+      </c>
+      <c r="E968" t="n">
+        <v>7896</v>
+      </c>
+      <c r="F968" t="n">
+        <v>11421</v>
+      </c>
+      <c r="G968" t="n">
+        <v>14313</v>
+      </c>
+      <c r="H968" t="n">
+        <v>16812</v>
+      </c>
+      <c r="I968" t="n">
+        <v>18681</v>
+      </c>
+      <c r="J968" t="n">
+        <v>20231</v>
+      </c>
+      <c r="K968" t="n">
+        <v>2959</v>
+      </c>
+      <c r="L968" t="n">
+        <v>884</v>
+      </c>
+      <c r="M968" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N968" t="n">
+        <v>350</v>
+      </c>
+      <c r="O968" t="n">
+        <v>3230</v>
+      </c>
+      <c r="P968" t="n">
+        <v>7591</v>
+      </c>
+      <c r="Q968" t="n">
+        <v>13337</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53027,7 +53082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B967"/>
+  <dimension ref="A1:B968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62702,6 +62757,16 @@
         <v>11802</v>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>11767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q968"/>
+  <dimension ref="A1:Q969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53071,6 +53071,61 @@
         <v>13337</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>28277</v>
+      </c>
+      <c r="C969" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D969" t="n">
+        <v>3948</v>
+      </c>
+      <c r="E969" t="n">
+        <v>7905</v>
+      </c>
+      <c r="F969" t="n">
+        <v>11430</v>
+      </c>
+      <c r="G969" t="n">
+        <v>14334</v>
+      </c>
+      <c r="H969" t="n">
+        <v>16827</v>
+      </c>
+      <c r="I969" t="n">
+        <v>18693</v>
+      </c>
+      <c r="J969" t="n">
+        <v>20250</v>
+      </c>
+      <c r="K969" t="n">
+        <v>2962</v>
+      </c>
+      <c r="L969" t="n">
+        <v>885</v>
+      </c>
+      <c r="M969" t="n">
+        <v>2242</v>
+      </c>
+      <c r="N969" t="n">
+        <v>353</v>
+      </c>
+      <c r="O969" t="n">
+        <v>3234</v>
+      </c>
+      <c r="P969" t="n">
+        <v>7597</v>
+      </c>
+      <c r="Q969" t="n">
+        <v>13349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53082,7 +53137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B968"/>
+  <dimension ref="A1:B969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62767,6 +62822,16 @@
         <v>11767</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>11758</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q969"/>
+  <dimension ref="A1:Q970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53126,6 +53126,61 @@
         <v>13349</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>28274</v>
+      </c>
+      <c r="C970" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D970" t="n">
+        <v>3950</v>
+      </c>
+      <c r="E970" t="n">
+        <v>7910</v>
+      </c>
+      <c r="F970" t="n">
+        <v>11433</v>
+      </c>
+      <c r="G970" t="n">
+        <v>14346</v>
+      </c>
+      <c r="H970" t="n">
+        <v>16839</v>
+      </c>
+      <c r="I970" t="n">
+        <v>18704</v>
+      </c>
+      <c r="J970" t="n">
+        <v>20255</v>
+      </c>
+      <c r="K970" t="n">
+        <v>2959</v>
+      </c>
+      <c r="L970" t="n">
+        <v>881</v>
+      </c>
+      <c r="M970" t="n">
+        <v>2239</v>
+      </c>
+      <c r="N970" t="n">
+        <v>352</v>
+      </c>
+      <c r="O970" t="n">
+        <v>3241</v>
+      </c>
+      <c r="P970" t="n">
+        <v>7608</v>
+      </c>
+      <c r="Q970" t="n">
+        <v>13365</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53137,7 +53192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B969"/>
+  <dimension ref="A1:B970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62832,6 +62887,16 @@
         <v>11758</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>11778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q970"/>
+  <dimension ref="A1:Q971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53181,6 +53181,61 @@
         <v>13365</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>28288</v>
+      </c>
+      <c r="C971" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D971" t="n">
+        <v>3950</v>
+      </c>
+      <c r="E971" t="n">
+        <v>7928</v>
+      </c>
+      <c r="F971" t="n">
+        <v>11451</v>
+      </c>
+      <c r="G971" t="n">
+        <v>14366</v>
+      </c>
+      <c r="H971" t="n">
+        <v>16863</v>
+      </c>
+      <c r="I971" t="n">
+        <v>18725</v>
+      </c>
+      <c r="J971" t="n">
+        <v>20270</v>
+      </c>
+      <c r="K971" t="n">
+        <v>2969</v>
+      </c>
+      <c r="L971" t="n">
+        <v>879</v>
+      </c>
+      <c r="M971" t="n">
+        <v>2236</v>
+      </c>
+      <c r="N971" t="n">
+        <v>351</v>
+      </c>
+      <c r="O971" t="n">
+        <v>3238</v>
+      </c>
+      <c r="P971" t="n">
+        <v>7614</v>
+      </c>
+      <c r="Q971" t="n">
+        <v>13389</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53192,7 +53247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B970"/>
+  <dimension ref="A1:B971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62897,6 +62952,16 @@
         <v>11778</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>11829</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q971"/>
+  <dimension ref="A1:Q972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53236,6 +53236,61 @@
         <v>13389</v>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>28334</v>
+      </c>
+      <c r="C972" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D972" t="n">
+        <v>3953</v>
+      </c>
+      <c r="E972" t="n">
+        <v>7939</v>
+      </c>
+      <c r="F972" t="n">
+        <v>11473</v>
+      </c>
+      <c r="G972" t="n">
+        <v>14400</v>
+      </c>
+      <c r="H972" t="n">
+        <v>16892</v>
+      </c>
+      <c r="I972" t="n">
+        <v>18763</v>
+      </c>
+      <c r="J972" t="n">
+        <v>20311</v>
+      </c>
+      <c r="K972" t="n">
+        <v>2973</v>
+      </c>
+      <c r="L972" t="n">
+        <v>883</v>
+      </c>
+      <c r="M972" t="n">
+        <v>2239</v>
+      </c>
+      <c r="N972" t="n">
+        <v>349</v>
+      </c>
+      <c r="O972" t="n">
+        <v>3245</v>
+      </c>
+      <c r="P972" t="n">
+        <v>7636</v>
+      </c>
+      <c r="Q972" t="n">
+        <v>13419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53247,7 +53302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B971"/>
+  <dimension ref="A1:B972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62962,6 +63017,16 @@
         <v>11829</v>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>11860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q972"/>
+  <dimension ref="A1:Q973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53291,6 +53291,61 @@
         <v>13419</v>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>28318</v>
+      </c>
+      <c r="C973" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D973" t="n">
+        <v>3947</v>
+      </c>
+      <c r="E973" t="n">
+        <v>7930</v>
+      </c>
+      <c r="F973" t="n">
+        <v>11460</v>
+      </c>
+      <c r="G973" t="n">
+        <v>14384</v>
+      </c>
+      <c r="H973" t="n">
+        <v>16863</v>
+      </c>
+      <c r="I973" t="n">
+        <v>18744</v>
+      </c>
+      <c r="J973" t="n">
+        <v>20292</v>
+      </c>
+      <c r="K973" t="n">
+        <v>2972</v>
+      </c>
+      <c r="L973" t="n">
+        <v>888</v>
+      </c>
+      <c r="M973" t="n">
+        <v>2240</v>
+      </c>
+      <c r="N973" t="n">
+        <v>347</v>
+      </c>
+      <c r="O973" t="n">
+        <v>3243</v>
+      </c>
+      <c r="P973" t="n">
+        <v>7631</v>
+      </c>
+      <c r="Q973" t="n">
+        <v>13401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53302,7 +53357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B972"/>
+  <dimension ref="A1:B973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63027,6 +63082,16 @@
         <v>11860</v>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>11817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q973"/>
+  <dimension ref="A1:Q974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53346,6 +53346,61 @@
         <v>13401</v>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>28303</v>
+      </c>
+      <c r="C974" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D974" t="n">
+        <v>3950</v>
+      </c>
+      <c r="E974" t="n">
+        <v>7923</v>
+      </c>
+      <c r="F974" t="n">
+        <v>11448</v>
+      </c>
+      <c r="G974" t="n">
+        <v>14367</v>
+      </c>
+      <c r="H974" t="n">
+        <v>16846</v>
+      </c>
+      <c r="I974" t="n">
+        <v>18731</v>
+      </c>
+      <c r="J974" t="n">
+        <v>20274</v>
+      </c>
+      <c r="K974" t="n">
+        <v>2981</v>
+      </c>
+      <c r="L974" t="n">
+        <v>887</v>
+      </c>
+      <c r="M974" t="n">
+        <v>2236</v>
+      </c>
+      <c r="N974" t="n">
+        <v>349</v>
+      </c>
+      <c r="O974" t="n">
+        <v>3238</v>
+      </c>
+      <c r="P974" t="n">
+        <v>7636</v>
+      </c>
+      <c r="Q974" t="n">
+        <v>13403</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53357,7 +53412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B973"/>
+  <dimension ref="A1:B974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63092,6 +63147,16 @@
         <v>11817</v>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>11786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q974"/>
+  <dimension ref="A1:Q975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53401,6 +53401,61 @@
         <v>13403</v>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>28288</v>
+      </c>
+      <c r="C975" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D975" t="n">
+        <v>3950</v>
+      </c>
+      <c r="E975" t="n">
+        <v>7916</v>
+      </c>
+      <c r="F975" t="n">
+        <v>11438</v>
+      </c>
+      <c r="G975" t="n">
+        <v>14360</v>
+      </c>
+      <c r="H975" t="n">
+        <v>16833</v>
+      </c>
+      <c r="I975" t="n">
+        <v>18717</v>
+      </c>
+      <c r="J975" t="n">
+        <v>20256</v>
+      </c>
+      <c r="K975" t="n">
+        <v>2983</v>
+      </c>
+      <c r="L975" t="n">
+        <v>879</v>
+      </c>
+      <c r="M975" t="n">
+        <v>2241</v>
+      </c>
+      <c r="N975" t="n">
+        <v>351</v>
+      </c>
+      <c r="O975" t="n">
+        <v>3244</v>
+      </c>
+      <c r="P975" t="n">
+        <v>7634</v>
+      </c>
+      <c r="Q975" t="n">
+        <v>13405</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53412,7 +53467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B974"/>
+  <dimension ref="A1:B975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63157,6 +63212,16 @@
         <v>11786</v>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>11766</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q975"/>
+  <dimension ref="A1:Q976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53456,6 +53456,61 @@
         <v>13405</v>
       </c>
     </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>28248</v>
+      </c>
+      <c r="C976" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D976" t="n">
+        <v>3951</v>
+      </c>
+      <c r="E976" t="n">
+        <v>7893</v>
+      </c>
+      <c r="F976" t="n">
+        <v>11415</v>
+      </c>
+      <c r="G976" t="n">
+        <v>14337</v>
+      </c>
+      <c r="H976" t="n">
+        <v>16795</v>
+      </c>
+      <c r="I976" t="n">
+        <v>18681</v>
+      </c>
+      <c r="J976" t="n">
+        <v>20218</v>
+      </c>
+      <c r="K976" t="n">
+        <v>2982</v>
+      </c>
+      <c r="L976" t="n">
+        <v>879</v>
+      </c>
+      <c r="M976" t="n">
+        <v>2242</v>
+      </c>
+      <c r="N976" t="n">
+        <v>350</v>
+      </c>
+      <c r="O976" t="n">
+        <v>3242</v>
+      </c>
+      <c r="P976" t="n">
+        <v>7614</v>
+      </c>
+      <c r="Q976" t="n">
+        <v>13378</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53467,7 +53522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B975"/>
+  <dimension ref="A1:B976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63222,6 +63277,16 @@
         <v>11766</v>
       </c>
     </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>11681</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q976"/>
+  <dimension ref="A1:Q977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53511,6 +53511,61 @@
         <v>13378</v>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>28270</v>
+      </c>
+      <c r="C977" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D977" t="n">
+        <v>3962</v>
+      </c>
+      <c r="E977" t="n">
+        <v>7905</v>
+      </c>
+      <c r="F977" t="n">
+        <v>11425</v>
+      </c>
+      <c r="G977" t="n">
+        <v>14349</v>
+      </c>
+      <c r="H977" t="n">
+        <v>16803</v>
+      </c>
+      <c r="I977" t="n">
+        <v>18689</v>
+      </c>
+      <c r="J977" t="n">
+        <v>20230</v>
+      </c>
+      <c r="K977" t="n">
+        <v>2997</v>
+      </c>
+      <c r="L977" t="n">
+        <v>877</v>
+      </c>
+      <c r="M977" t="n">
+        <v>2244</v>
+      </c>
+      <c r="N977" t="n">
+        <v>349</v>
+      </c>
+      <c r="O977" t="n">
+        <v>3252</v>
+      </c>
+      <c r="P977" t="n">
+        <v>7626</v>
+      </c>
+      <c r="Q977" t="n">
+        <v>13393</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53522,7 +53577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B976"/>
+  <dimension ref="A1:B977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63287,6 +63342,16 @@
         <v>11681</v>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>11663</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q977"/>
+  <dimension ref="A1:Q978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53566,6 +53566,61 @@
         <v>13393</v>
       </c>
     </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>28310</v>
+      </c>
+      <c r="C978" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D978" t="n">
+        <v>3965</v>
+      </c>
+      <c r="E978" t="n">
+        <v>7913</v>
+      </c>
+      <c r="F978" t="n">
+        <v>11438</v>
+      </c>
+      <c r="G978" t="n">
+        <v>14361</v>
+      </c>
+      <c r="H978" t="n">
+        <v>16827</v>
+      </c>
+      <c r="I978" t="n">
+        <v>18709</v>
+      </c>
+      <c r="J978" t="n">
+        <v>20252</v>
+      </c>
+      <c r="K978" t="n">
+        <v>2998</v>
+      </c>
+      <c r="L978" t="n">
+        <v>887</v>
+      </c>
+      <c r="M978" t="n">
+        <v>2246</v>
+      </c>
+      <c r="N978" t="n">
+        <v>348</v>
+      </c>
+      <c r="O978" t="n">
+        <v>3253</v>
+      </c>
+      <c r="P978" t="n">
+        <v>7645</v>
+      </c>
+      <c r="Q978" t="n">
+        <v>13417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53577,7 +53632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B977"/>
+  <dimension ref="A1:B978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63352,6 +63407,16 @@
         <v>11663</v>
       </c>
     </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>11662</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q978"/>
+  <dimension ref="A1:Q979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53621,6 +53621,61 @@
         <v>13417</v>
       </c>
     </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>28327</v>
+      </c>
+      <c r="C979" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D979" t="n">
+        <v>3956</v>
+      </c>
+      <c r="E979" t="n">
+        <v>7901</v>
+      </c>
+      <c r="F979" t="n">
+        <v>11431</v>
+      </c>
+      <c r="G979" t="n">
+        <v>14372</v>
+      </c>
+      <c r="H979" t="n">
+        <v>16841</v>
+      </c>
+      <c r="I979" t="n">
+        <v>18728</v>
+      </c>
+      <c r="J979" t="n">
+        <v>20267</v>
+      </c>
+      <c r="K979" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L979" t="n">
+        <v>884</v>
+      </c>
+      <c r="M979" t="n">
+        <v>2245</v>
+      </c>
+      <c r="N979" t="n">
+        <v>348</v>
+      </c>
+      <c r="O979" t="n">
+        <v>3255</v>
+      </c>
+      <c r="P979" t="n">
+        <v>7658</v>
+      </c>
+      <c r="Q979" t="n">
+        <v>13428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53632,7 +53687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B978"/>
+  <dimension ref="A1:B979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63417,6 +63472,16 @@
         <v>11662</v>
       </c>
     </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>11666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q979"/>
+  <dimension ref="A1:Q980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53676,6 +53676,61 @@
         <v>13428</v>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>28337</v>
+      </c>
+      <c r="C980" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D980" t="n">
+        <v>3961</v>
+      </c>
+      <c r="E980" t="n">
+        <v>7896</v>
+      </c>
+      <c r="F980" t="n">
+        <v>11432</v>
+      </c>
+      <c r="G980" t="n">
+        <v>14377</v>
+      </c>
+      <c r="H980" t="n">
+        <v>16843</v>
+      </c>
+      <c r="I980" t="n">
+        <v>18736</v>
+      </c>
+      <c r="J980" t="n">
+        <v>20269</v>
+      </c>
+      <c r="K980" t="n">
+        <v>2996</v>
+      </c>
+      <c r="L980" t="n">
+        <v>883</v>
+      </c>
+      <c r="M980" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N980" t="n">
+        <v>346</v>
+      </c>
+      <c r="O980" t="n">
+        <v>3256</v>
+      </c>
+      <c r="P980" t="n">
+        <v>7662</v>
+      </c>
+      <c r="Q980" t="n">
+        <v>13444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53687,7 +53742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B979"/>
+  <dimension ref="A1:B980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63482,6 +63537,16 @@
         <v>11666</v>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>11657</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q980"/>
+  <dimension ref="A1:Q981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53731,6 +53731,61 @@
         <v>13444</v>
       </c>
     </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>28366</v>
+      </c>
+      <c r="C981" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D981" t="n">
+        <v>3963</v>
+      </c>
+      <c r="E981" t="n">
+        <v>7900</v>
+      </c>
+      <c r="F981" t="n">
+        <v>11442</v>
+      </c>
+      <c r="G981" t="n">
+        <v>14391</v>
+      </c>
+      <c r="H981" t="n">
+        <v>16865</v>
+      </c>
+      <c r="I981" t="n">
+        <v>18762</v>
+      </c>
+      <c r="J981" t="n">
+        <v>20298</v>
+      </c>
+      <c r="K981" t="n">
+        <v>3006</v>
+      </c>
+      <c r="L981" t="n">
+        <v>881</v>
+      </c>
+      <c r="M981" t="n">
+        <v>2251</v>
+      </c>
+      <c r="N981" t="n">
+        <v>344</v>
+      </c>
+      <c r="O981" t="n">
+        <v>3257</v>
+      </c>
+      <c r="P981" t="n">
+        <v>7673</v>
+      </c>
+      <c r="Q981" t="n">
+        <v>13468</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53742,7 +53797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B980"/>
+  <dimension ref="A1:B981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63547,6 +63602,16 @@
         <v>11657</v>
       </c>
     </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>11651</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q981"/>
+  <dimension ref="A1:Q982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53786,6 +53786,61 @@
         <v>13468</v>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>28349</v>
+      </c>
+      <c r="C982" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D982" t="n">
+        <v>3950</v>
+      </c>
+      <c r="E982" t="n">
+        <v>7884</v>
+      </c>
+      <c r="F982" t="n">
+        <v>11429</v>
+      </c>
+      <c r="G982" t="n">
+        <v>14382</v>
+      </c>
+      <c r="H982" t="n">
+        <v>16850</v>
+      </c>
+      <c r="I982" t="n">
+        <v>18742</v>
+      </c>
+      <c r="J982" t="n">
+        <v>20282</v>
+      </c>
+      <c r="K982" t="n">
+        <v>2995</v>
+      </c>
+      <c r="L982" t="n">
+        <v>885</v>
+      </c>
+      <c r="M982" t="n">
+        <v>2258</v>
+      </c>
+      <c r="N982" t="n">
+        <v>343</v>
+      </c>
+      <c r="O982" t="n">
+        <v>3247</v>
+      </c>
+      <c r="P982" t="n">
+        <v>7669</v>
+      </c>
+      <c r="Q982" t="n">
+        <v>13464</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53797,7 +53852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B981"/>
+  <dimension ref="A1:B982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63612,6 +63667,16 @@
         <v>11651</v>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>11664</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q982"/>
+  <dimension ref="A1:Q983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53841,6 +53841,61 @@
         <v>13464</v>
       </c>
     </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>28340</v>
+      </c>
+      <c r="C983" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D983" t="n">
+        <v>3957</v>
+      </c>
+      <c r="E983" t="n">
+        <v>7887</v>
+      </c>
+      <c r="F983" t="n">
+        <v>11431</v>
+      </c>
+      <c r="G983" t="n">
+        <v>14388</v>
+      </c>
+      <c r="H983" t="n">
+        <v>16845</v>
+      </c>
+      <c r="I983" t="n">
+        <v>18735</v>
+      </c>
+      <c r="J983" t="n">
+        <v>20279</v>
+      </c>
+      <c r="K983" t="n">
+        <v>2997</v>
+      </c>
+      <c r="L983" t="n">
+        <v>886</v>
+      </c>
+      <c r="M983" t="n">
+        <v>2256</v>
+      </c>
+      <c r="N983" t="n">
+        <v>346</v>
+      </c>
+      <c r="O983" t="n">
+        <v>3252</v>
+      </c>
+      <c r="P983" t="n">
+        <v>7675</v>
+      </c>
+      <c r="Q983" t="n">
+        <v>13469</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53852,7 +53907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B982"/>
+  <dimension ref="A1:B983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63677,6 +63732,16 @@
         <v>11664</v>
       </c>
     </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>11704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q983"/>
+  <dimension ref="A1:Q984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53896,6 +53896,61 @@
         <v>13469</v>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>28349</v>
+      </c>
+      <c r="C984" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D984" t="n">
+        <v>3955</v>
+      </c>
+      <c r="E984" t="n">
+        <v>7883</v>
+      </c>
+      <c r="F984" t="n">
+        <v>11432</v>
+      </c>
+      <c r="G984" t="n">
+        <v>14392</v>
+      </c>
+      <c r="H984" t="n">
+        <v>16852</v>
+      </c>
+      <c r="I984" t="n">
+        <v>18746</v>
+      </c>
+      <c r="J984" t="n">
+        <v>20292</v>
+      </c>
+      <c r="K984" t="n">
+        <v>2995</v>
+      </c>
+      <c r="L984" t="n">
+        <v>893</v>
+      </c>
+      <c r="M984" t="n">
+        <v>2252</v>
+      </c>
+      <c r="N984" t="n">
+        <v>344</v>
+      </c>
+      <c r="O984" t="n">
+        <v>3244</v>
+      </c>
+      <c r="P984" t="n">
+        <v>7668</v>
+      </c>
+      <c r="Q984" t="n">
+        <v>13476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53907,7 +53962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B983"/>
+  <dimension ref="A1:B984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63742,6 +63797,16 @@
         <v>11704</v>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>11680</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q984"/>
+  <dimension ref="A1:Q985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53951,6 +53951,61 @@
         <v>13476</v>
       </c>
     </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>28343</v>
+      </c>
+      <c r="C985" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D985" t="n">
+        <v>3939</v>
+      </c>
+      <c r="E985" t="n">
+        <v>7864</v>
+      </c>
+      <c r="F985" t="n">
+        <v>11418</v>
+      </c>
+      <c r="G985" t="n">
+        <v>14373</v>
+      </c>
+      <c r="H985" t="n">
+        <v>16832</v>
+      </c>
+      <c r="I985" t="n">
+        <v>18733</v>
+      </c>
+      <c r="J985" t="n">
+        <v>20286</v>
+      </c>
+      <c r="K985" t="n">
+        <v>2993</v>
+      </c>
+      <c r="L985" t="n">
+        <v>898</v>
+      </c>
+      <c r="M985" t="n">
+        <v>2252</v>
+      </c>
+      <c r="N985" t="n">
+        <v>341</v>
+      </c>
+      <c r="O985" t="n">
+        <v>3243</v>
+      </c>
+      <c r="P985" t="n">
+        <v>7659</v>
+      </c>
+      <c r="Q985" t="n">
+        <v>13467</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53962,7 +54017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B984"/>
+  <dimension ref="A1:B985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63807,6 +63862,16 @@
         <v>11680</v>
       </c>
     </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>11718</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q985"/>
+  <dimension ref="A1:Q986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54006,6 +54006,61 @@
         <v>13467</v>
       </c>
     </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>28373</v>
+      </c>
+      <c r="C986" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D986" t="n">
+        <v>3945</v>
+      </c>
+      <c r="E986" t="n">
+        <v>7874</v>
+      </c>
+      <c r="F986" t="n">
+        <v>11431</v>
+      </c>
+      <c r="G986" t="n">
+        <v>14389</v>
+      </c>
+      <c r="H986" t="n">
+        <v>16841</v>
+      </c>
+      <c r="I986" t="n">
+        <v>18746</v>
+      </c>
+      <c r="J986" t="n">
+        <v>20297</v>
+      </c>
+      <c r="K986" t="n">
+        <v>2998</v>
+      </c>
+      <c r="L986" t="n">
+        <v>902</v>
+      </c>
+      <c r="M986" t="n">
+        <v>2257</v>
+      </c>
+      <c r="N986" t="n">
+        <v>342</v>
+      </c>
+      <c r="O986" t="n">
+        <v>3261</v>
+      </c>
+      <c r="P986" t="n">
+        <v>7678</v>
+      </c>
+      <c r="Q986" t="n">
+        <v>13477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54017,7 +54072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B985"/>
+  <dimension ref="A1:B986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63872,6 +63927,16 @@
         <v>11718</v>
       </c>
     </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>11731</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q986"/>
+  <dimension ref="A1:Q987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54061,6 +54061,61 @@
         <v>13477</v>
       </c>
     </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>28381</v>
+      </c>
+      <c r="C987" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D987" t="n">
+        <v>3947</v>
+      </c>
+      <c r="E987" t="n">
+        <v>7870</v>
+      </c>
+      <c r="F987" t="n">
+        <v>11432</v>
+      </c>
+      <c r="G987" t="n">
+        <v>14389</v>
+      </c>
+      <c r="H987" t="n">
+        <v>16843</v>
+      </c>
+      <c r="I987" t="n">
+        <v>18744</v>
+      </c>
+      <c r="J987" t="n">
+        <v>20304</v>
+      </c>
+      <c r="K987" t="n">
+        <v>3002</v>
+      </c>
+      <c r="L987" t="n">
+        <v>898</v>
+      </c>
+      <c r="M987" t="n">
+        <v>2256</v>
+      </c>
+      <c r="N987" t="n">
+        <v>341</v>
+      </c>
+      <c r="O987" t="n">
+        <v>3255</v>
+      </c>
+      <c r="P987" t="n">
+        <v>7689</v>
+      </c>
+      <c r="Q987" t="n">
+        <v>13483</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54072,7 +54127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B986"/>
+  <dimension ref="A1:B987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63937,6 +63992,16 @@
         <v>11731</v>
       </c>
     </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>11733</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q987"/>
+  <dimension ref="A1:Q988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54116,6 +54116,61 @@
         <v>13483</v>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>28390</v>
+      </c>
+      <c r="C988" t="n">
+        <v>1071</v>
+      </c>
+      <c r="D988" t="n">
+        <v>3953</v>
+      </c>
+      <c r="E988" t="n">
+        <v>7864</v>
+      </c>
+      <c r="F988" t="n">
+        <v>11428</v>
+      </c>
+      <c r="G988" t="n">
+        <v>14383</v>
+      </c>
+      <c r="H988" t="n">
+        <v>16839</v>
+      </c>
+      <c r="I988" t="n">
+        <v>18739</v>
+      </c>
+      <c r="J988" t="n">
+        <v>20306</v>
+      </c>
+      <c r="K988" t="n">
+        <v>3007</v>
+      </c>
+      <c r="L988" t="n">
+        <v>896</v>
+      </c>
+      <c r="M988" t="n">
+        <v>2262</v>
+      </c>
+      <c r="N988" t="n">
+        <v>341</v>
+      </c>
+      <c r="O988" t="n">
+        <v>3268</v>
+      </c>
+      <c r="P988" t="n">
+        <v>7695</v>
+      </c>
+      <c r="Q988" t="n">
+        <v>13486</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54127,7 +54182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B987"/>
+  <dimension ref="A1:B988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64002,6 +64057,16 @@
         <v>11733</v>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>11752</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q988"/>
+  <dimension ref="A1:Q989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54171,6 +54171,61 @@
         <v>13486</v>
       </c>
     </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>28388</v>
+      </c>
+      <c r="C989" t="n">
+        <v>1073</v>
+      </c>
+      <c r="D989" t="n">
+        <v>3950</v>
+      </c>
+      <c r="E989" t="n">
+        <v>7856</v>
+      </c>
+      <c r="F989" t="n">
+        <v>11406</v>
+      </c>
+      <c r="G989" t="n">
+        <v>14373</v>
+      </c>
+      <c r="H989" t="n">
+        <v>16838</v>
+      </c>
+      <c r="I989" t="n">
+        <v>18739</v>
+      </c>
+      <c r="J989" t="n">
+        <v>20310</v>
+      </c>
+      <c r="K989" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L989" t="n">
+        <v>893</v>
+      </c>
+      <c r="M989" t="n">
+        <v>2264</v>
+      </c>
+      <c r="N989" t="n">
+        <v>341</v>
+      </c>
+      <c r="O989" t="n">
+        <v>3274</v>
+      </c>
+      <c r="P989" t="n">
+        <v>7701</v>
+      </c>
+      <c r="Q989" t="n">
+        <v>13484</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54182,7 +54237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B988"/>
+  <dimension ref="A1:B989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64067,6 +64122,16 @@
         <v>11752</v>
       </c>
     </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>11795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q989"/>
+  <dimension ref="A1:Q990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54226,6 +54226,61 @@
         <v>13484</v>
       </c>
     </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>28376</v>
+      </c>
+      <c r="C990" t="n">
+        <v>1071</v>
+      </c>
+      <c r="D990" t="n">
+        <v>3948</v>
+      </c>
+      <c r="E990" t="n">
+        <v>7862</v>
+      </c>
+      <c r="F990" t="n">
+        <v>11398</v>
+      </c>
+      <c r="G990" t="n">
+        <v>14372</v>
+      </c>
+      <c r="H990" t="n">
+        <v>16837</v>
+      </c>
+      <c r="I990" t="n">
+        <v>18733</v>
+      </c>
+      <c r="J990" t="n">
+        <v>20304</v>
+      </c>
+      <c r="K990" t="n">
+        <v>3001</v>
+      </c>
+      <c r="L990" t="n">
+        <v>893</v>
+      </c>
+      <c r="M990" t="n">
+        <v>2267</v>
+      </c>
+      <c r="N990" t="n">
+        <v>342</v>
+      </c>
+      <c r="O990" t="n">
+        <v>3270</v>
+      </c>
+      <c r="P990" t="n">
+        <v>7703</v>
+      </c>
+      <c r="Q990" t="n">
+        <v>13487</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54237,7 +54292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B989"/>
+  <dimension ref="A1:B990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64132,6 +64187,16 @@
         <v>11795</v>
       </c>
     </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>11850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q990"/>
+  <dimension ref="A1:Q991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54281,6 +54281,61 @@
         <v>13487</v>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>28408</v>
+      </c>
+      <c r="C991" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D991" t="n">
+        <v>3935</v>
+      </c>
+      <c r="E991" t="n">
+        <v>7848</v>
+      </c>
+      <c r="F991" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G991" t="n">
+        <v>14377</v>
+      </c>
+      <c r="H991" t="n">
+        <v>16847</v>
+      </c>
+      <c r="I991" t="n">
+        <v>18754</v>
+      </c>
+      <c r="J991" t="n">
+        <v>20321</v>
+      </c>
+      <c r="K991" t="n">
+        <v>3001</v>
+      </c>
+      <c r="L991" t="n">
+        <v>895</v>
+      </c>
+      <c r="M991" t="n">
+        <v>2276</v>
+      </c>
+      <c r="N991" t="n">
+        <v>344</v>
+      </c>
+      <c r="O991" t="n">
+        <v>3267</v>
+      </c>
+      <c r="P991" t="n">
+        <v>7706</v>
+      </c>
+      <c r="Q991" t="n">
+        <v>13505</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54292,7 +54347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B990"/>
+  <dimension ref="A1:B991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64197,6 +64252,16 @@
         <v>11850</v>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>11882</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q991"/>
+  <dimension ref="A1:Q992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54336,6 +54336,61 @@
         <v>13505</v>
       </c>
     </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>28419</v>
+      </c>
+      <c r="C992" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D992" t="n">
+        <v>3936</v>
+      </c>
+      <c r="E992" t="n">
+        <v>7848</v>
+      </c>
+      <c r="F992" t="n">
+        <v>11402</v>
+      </c>
+      <c r="G992" t="n">
+        <v>14383</v>
+      </c>
+      <c r="H992" t="n">
+        <v>16851</v>
+      </c>
+      <c r="I992" t="n">
+        <v>18770</v>
+      </c>
+      <c r="J992" t="n">
+        <v>20336</v>
+      </c>
+      <c r="K992" t="n">
+        <v>3006</v>
+      </c>
+      <c r="L992" t="n">
+        <v>893</v>
+      </c>
+      <c r="M992" t="n">
+        <v>2271</v>
+      </c>
+      <c r="N992" t="n">
+        <v>341</v>
+      </c>
+      <c r="O992" t="n">
+        <v>3270</v>
+      </c>
+      <c r="P992" t="n">
+        <v>7712</v>
+      </c>
+      <c r="Q992" t="n">
+        <v>13512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54347,7 +54402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B991"/>
+  <dimension ref="A1:B992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64262,6 +64317,16 @@
         <v>11882</v>
       </c>
     </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>11872</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q992"/>
+  <dimension ref="A1:Q993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54391,6 +54391,61 @@
         <v>13512</v>
       </c>
     </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>28444</v>
+      </c>
+      <c r="C993" t="n">
+        <v>1066</v>
+      </c>
+      <c r="D993" t="n">
+        <v>3951</v>
+      </c>
+      <c r="E993" t="n">
+        <v>7858</v>
+      </c>
+      <c r="F993" t="n">
+        <v>11412</v>
+      </c>
+      <c r="G993" t="n">
+        <v>14389</v>
+      </c>
+      <c r="H993" t="n">
+        <v>16858</v>
+      </c>
+      <c r="I993" t="n">
+        <v>18786</v>
+      </c>
+      <c r="J993" t="n">
+        <v>20354</v>
+      </c>
+      <c r="K993" t="n">
+        <v>3005</v>
+      </c>
+      <c r="L993" t="n">
+        <v>893</v>
+      </c>
+      <c r="M993" t="n">
+        <v>2277</v>
+      </c>
+      <c r="N993" t="n">
+        <v>341</v>
+      </c>
+      <c r="O993" t="n">
+        <v>3278</v>
+      </c>
+      <c r="P993" t="n">
+        <v>7720</v>
+      </c>
+      <c r="Q993" t="n">
+        <v>13523</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54402,7 +54457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B992"/>
+  <dimension ref="A1:B993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64327,6 +64382,16 @@
         <v>11872</v>
       </c>
     </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>11871</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q993"/>
+  <dimension ref="A1:Q994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54446,6 +54446,61 @@
         <v>13523</v>
       </c>
     </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>28392</v>
+      </c>
+      <c r="C994" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D994" t="n">
+        <v>3933</v>
+      </c>
+      <c r="E994" t="n">
+        <v>7838</v>
+      </c>
+      <c r="F994" t="n">
+        <v>11381</v>
+      </c>
+      <c r="G994" t="n">
+        <v>14340</v>
+      </c>
+      <c r="H994" t="n">
+        <v>16814</v>
+      </c>
+      <c r="I994" t="n">
+        <v>18735</v>
+      </c>
+      <c r="J994" t="n">
+        <v>20302</v>
+      </c>
+      <c r="K994" t="n">
+        <v>3004</v>
+      </c>
+      <c r="L994" t="n">
+        <v>895</v>
+      </c>
+      <c r="M994" t="n">
+        <v>2280</v>
+      </c>
+      <c r="N994" t="n">
+        <v>341</v>
+      </c>
+      <c r="O994" t="n">
+        <v>3280</v>
+      </c>
+      <c r="P994" t="n">
+        <v>7694</v>
+      </c>
+      <c r="Q994" t="n">
+        <v>13481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54457,7 +54512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B993"/>
+  <dimension ref="A1:B994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64392,6 +64447,16 @@
         <v>11871</v>
       </c>
     </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>11789</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q994"/>
+  <dimension ref="A1:Q995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54501,6 +54501,61 @@
         <v>13481</v>
       </c>
     </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>28336</v>
+      </c>
+      <c r="C995" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D995" t="n">
+        <v>3906</v>
+      </c>
+      <c r="E995" t="n">
+        <v>7790</v>
+      </c>
+      <c r="F995" t="n">
+        <v>11328</v>
+      </c>
+      <c r="G995" t="n">
+        <v>14293</v>
+      </c>
+      <c r="H995" t="n">
+        <v>16762</v>
+      </c>
+      <c r="I995" t="n">
+        <v>18673</v>
+      </c>
+      <c r="J995" t="n">
+        <v>20234</v>
+      </c>
+      <c r="K995" t="n">
+        <v>3003</v>
+      </c>
+      <c r="L995" t="n">
+        <v>893</v>
+      </c>
+      <c r="M995" t="n">
+        <v>2291</v>
+      </c>
+      <c r="N995" t="n">
+        <v>341</v>
+      </c>
+      <c r="O995" t="n">
+        <v>3278</v>
+      </c>
+      <c r="P995" t="n">
+        <v>7690</v>
+      </c>
+      <c r="Q995" t="n">
+        <v>13459</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54512,7 +54567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B994"/>
+  <dimension ref="A1:B995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64457,6 +64512,16 @@
         <v>11789</v>
       </c>
     </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>11811</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q995"/>
+  <dimension ref="A1:Q996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54556,6 +54556,61 @@
         <v>13459</v>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>28364</v>
+      </c>
+      <c r="C996" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D996" t="n">
+        <v>3907</v>
+      </c>
+      <c r="E996" t="n">
+        <v>7788</v>
+      </c>
+      <c r="F996" t="n">
+        <v>11336</v>
+      </c>
+      <c r="G996" t="n">
+        <v>14309</v>
+      </c>
+      <c r="H996" t="n">
+        <v>16777</v>
+      </c>
+      <c r="I996" t="n">
+        <v>18693</v>
+      </c>
+      <c r="J996" t="n">
+        <v>20258</v>
+      </c>
+      <c r="K996" t="n">
+        <v>3011</v>
+      </c>
+      <c r="L996" t="n">
+        <v>891</v>
+      </c>
+      <c r="M996" t="n">
+        <v>2291</v>
+      </c>
+      <c r="N996" t="n">
+        <v>344</v>
+      </c>
+      <c r="O996" t="n">
+        <v>3292</v>
+      </c>
+      <c r="P996" t="n">
+        <v>7717</v>
+      </c>
+      <c r="Q996" t="n">
+        <v>13497</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54567,7 +54622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B995"/>
+  <dimension ref="A1:B996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64522,6 +64577,16 @@
         <v>11811</v>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>11800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q996"/>
+  <dimension ref="A1:Q997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54611,6 +54611,61 @@
         <v>13497</v>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>28383</v>
+      </c>
+      <c r="C997" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D997" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E997" t="n">
+        <v>7793</v>
+      </c>
+      <c r="F997" t="n">
+        <v>11335</v>
+      </c>
+      <c r="G997" t="n">
+        <v>14313</v>
+      </c>
+      <c r="H997" t="n">
+        <v>16786</v>
+      </c>
+      <c r="I997" t="n">
+        <v>18707</v>
+      </c>
+      <c r="J997" t="n">
+        <v>20276</v>
+      </c>
+      <c r="K997" t="n">
+        <v>3010</v>
+      </c>
+      <c r="L997" t="n">
+        <v>891</v>
+      </c>
+      <c r="M997" t="n">
+        <v>2293</v>
+      </c>
+      <c r="N997" t="n">
+        <v>343</v>
+      </c>
+      <c r="O997" t="n">
+        <v>3290</v>
+      </c>
+      <c r="P997" t="n">
+        <v>7729</v>
+      </c>
+      <c r="Q997" t="n">
+        <v>13508</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54622,7 +54677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B996"/>
+  <dimension ref="A1:B997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64587,6 +64642,16 @@
         <v>11800</v>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>11803</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q997"/>
+  <dimension ref="A1:Q998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54666,6 +54666,61 @@
         <v>13508</v>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>28409</v>
+      </c>
+      <c r="C998" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D998" t="n">
+        <v>3906</v>
+      </c>
+      <c r="E998" t="n">
+        <v>7776</v>
+      </c>
+      <c r="F998" t="n">
+        <v>11309</v>
+      </c>
+      <c r="G998" t="n">
+        <v>14299</v>
+      </c>
+      <c r="H998" t="n">
+        <v>16776</v>
+      </c>
+      <c r="I998" t="n">
+        <v>18706</v>
+      </c>
+      <c r="J998" t="n">
+        <v>20276</v>
+      </c>
+      <c r="K998" t="n">
+        <v>3024</v>
+      </c>
+      <c r="L998" t="n">
+        <v>897</v>
+      </c>
+      <c r="M998" t="n">
+        <v>2292</v>
+      </c>
+      <c r="N998" t="n">
+        <v>342</v>
+      </c>
+      <c r="O998" t="n">
+        <v>3291</v>
+      </c>
+      <c r="P998" t="n">
+        <v>7738</v>
+      </c>
+      <c r="Q998" t="n">
+        <v>13523</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54677,7 +54732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B997"/>
+  <dimension ref="A1:B998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64652,6 +64707,16 @@
         <v>11803</v>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>11795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q998"/>
+  <dimension ref="A1:Q999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54721,6 +54721,61 @@
         <v>13523</v>
       </c>
     </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>28446</v>
+      </c>
+      <c r="C999" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D999" t="n">
+        <v>3907</v>
+      </c>
+      <c r="E999" t="n">
+        <v>7777</v>
+      </c>
+      <c r="F999" t="n">
+        <v>11321</v>
+      </c>
+      <c r="G999" t="n">
+        <v>14319</v>
+      </c>
+      <c r="H999" t="n">
+        <v>16806</v>
+      </c>
+      <c r="I999" t="n">
+        <v>18743</v>
+      </c>
+      <c r="J999" t="n">
+        <v>20311</v>
+      </c>
+      <c r="K999" t="n">
+        <v>3025</v>
+      </c>
+      <c r="L999" t="n">
+        <v>899</v>
+      </c>
+      <c r="M999" t="n">
+        <v>2293</v>
+      </c>
+      <c r="N999" t="n">
+        <v>344</v>
+      </c>
+      <c r="O999" t="n">
+        <v>3301</v>
+      </c>
+      <c r="P999" t="n">
+        <v>7745</v>
+      </c>
+      <c r="Q999" t="n">
+        <v>13541</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54732,7 +54787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B998"/>
+  <dimension ref="A1:B999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64717,6 +64772,16 @@
         <v>11795</v>
       </c>
     </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>11842</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q999"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54776,6 +54776,61 @@
         <v>13541</v>
       </c>
     </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>28474</v>
+      </c>
+      <c r="C1000" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>3917</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>7791</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>11329</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>14338</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>16814</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>18757</v>
+      </c>
+      <c r="J1000" t="n">
+        <v>20328</v>
+      </c>
+      <c r="K1000" t="n">
+        <v>3032</v>
+      </c>
+      <c r="L1000" t="n">
+        <v>900</v>
+      </c>
+      <c r="M1000" t="n">
+        <v>2299</v>
+      </c>
+      <c r="N1000" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1000" t="n">
+        <v>3304</v>
+      </c>
+      <c r="P1000" t="n">
+        <v>7751</v>
+      </c>
+      <c r="Q1000" t="n">
+        <v>13564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54787,7 +54842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B999"/>
+  <dimension ref="A1:B1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64782,6 +64837,16 @@
         <v>11842</v>
       </c>
     </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>11866</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:Q1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54831,6 +54831,61 @@
         <v>13564</v>
       </c>
     </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>28462</v>
+      </c>
+      <c r="C1001" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>3909</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>7778</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>11328</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>14325</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>16809</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>18741</v>
+      </c>
+      <c r="J1001" t="n">
+        <v>20312</v>
+      </c>
+      <c r="K1001" t="n">
+        <v>3044</v>
+      </c>
+      <c r="L1001" t="n">
+        <v>899</v>
+      </c>
+      <c r="M1001" t="n">
+        <v>2294</v>
+      </c>
+      <c r="N1001" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1001" t="n">
+        <v>3299</v>
+      </c>
+      <c r="P1001" t="n">
+        <v>7752</v>
+      </c>
+      <c r="Q1001" t="n">
+        <v>13565</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54842,7 +54897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:B1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64847,6 +64902,16 @@
         <v>11866</v>
       </c>
     </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>11871</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1001"/>
+  <dimension ref="A1:Q1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54886,6 +54886,61 @@
         <v>13565</v>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>28470</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>3909</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>7781</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>11341</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>14343</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>16830</v>
+      </c>
+      <c r="I1002" t="n">
+        <v>18758</v>
+      </c>
+      <c r="J1002" t="n">
+        <v>20326</v>
+      </c>
+      <c r="K1002" t="n">
+        <v>3052</v>
+      </c>
+      <c r="L1002" t="n">
+        <v>893</v>
+      </c>
+      <c r="M1002" t="n">
+        <v>2299</v>
+      </c>
+      <c r="N1002" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1002" t="n">
+        <v>3298</v>
+      </c>
+      <c r="P1002" t="n">
+        <v>7756</v>
+      </c>
+      <c r="Q1002" t="n">
+        <v>13581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54897,7 +54952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1001"/>
+  <dimension ref="A1:B1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64912,6 +64967,16 @@
         <v>11871</v>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>11868</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1002"/>
+  <dimension ref="A1:Q1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54941,6 +54941,61 @@
         <v>13581</v>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>28476</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>3898</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>7768</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>11336</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>14350</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>16844</v>
+      </c>
+      <c r="I1003" t="n">
+        <v>18770</v>
+      </c>
+      <c r="J1003" t="n">
+        <v>20325</v>
+      </c>
+      <c r="K1003" t="n">
+        <v>3049</v>
+      </c>
+      <c r="L1003" t="n">
+        <v>897</v>
+      </c>
+      <c r="M1003" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N1003" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1003" t="n">
+        <v>3303</v>
+      </c>
+      <c r="P1003" t="n">
+        <v>7767</v>
+      </c>
+      <c r="Q1003" t="n">
+        <v>13587</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54952,7 +55007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1002"/>
+  <dimension ref="A1:B1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64977,6 +65032,16 @@
         <v>11868</v>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>11885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1003"/>
+  <dimension ref="A1:Q1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54996,6 +54996,61 @@
         <v>13587</v>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>28533</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>7773</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>11349</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>14379</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>16875</v>
+      </c>
+      <c r="I1004" t="n">
+        <v>18805</v>
+      </c>
+      <c r="J1004" t="n">
+        <v>20370</v>
+      </c>
+      <c r="K1004" t="n">
+        <v>3049</v>
+      </c>
+      <c r="L1004" t="n">
+        <v>898</v>
+      </c>
+      <c r="M1004" t="n">
+        <v>2311</v>
+      </c>
+      <c r="N1004" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1004" t="n">
+        <v>3303</v>
+      </c>
+      <c r="P1004" t="n">
+        <v>7780</v>
+      </c>
+      <c r="Q1004" t="n">
+        <v>13615</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55007,7 +55062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1003"/>
+  <dimension ref="A1:B1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65042,6 +65097,16 @@
         <v>11885</v>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>11952</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1004"/>
+  <dimension ref="A1:Q1005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55051,6 +55051,61 @@
         <v>13615</v>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>28536</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>3896</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>7768</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>11346</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>14377</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>16878</v>
+      </c>
+      <c r="I1005" t="n">
+        <v>18809</v>
+      </c>
+      <c r="J1005" t="n">
+        <v>20373</v>
+      </c>
+      <c r="K1005" t="n">
+        <v>3051</v>
+      </c>
+      <c r="L1005" t="n">
+        <v>896</v>
+      </c>
+      <c r="M1005" t="n">
+        <v>2312</v>
+      </c>
+      <c r="N1005" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1005" t="n">
+        <v>3306</v>
+      </c>
+      <c r="P1005" t="n">
+        <v>7788</v>
+      </c>
+      <c r="Q1005" t="n">
+        <v>13631</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55062,7 +55117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1004"/>
+  <dimension ref="A1:B1005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65107,6 +65162,16 @@
         <v>11952</v>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>11930</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1005"/>
+  <dimension ref="A1:Q1006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55106,6 +55106,61 @@
         <v>13631</v>
       </c>
     </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>28559</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>3891</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>7767</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>11346</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>14387</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>16884</v>
+      </c>
+      <c r="I1006" t="n">
+        <v>18818</v>
+      </c>
+      <c r="J1006" t="n">
+        <v>20387</v>
+      </c>
+      <c r="K1006" t="n">
+        <v>3055</v>
+      </c>
+      <c r="L1006" t="n">
+        <v>901</v>
+      </c>
+      <c r="M1006" t="n">
+        <v>2319</v>
+      </c>
+      <c r="N1006" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1006" t="n">
+        <v>3308</v>
+      </c>
+      <c r="P1006" t="n">
+        <v>7794</v>
+      </c>
+      <c r="Q1006" t="n">
+        <v>13648</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55117,7 +55172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1005"/>
+  <dimension ref="A1:B1006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65172,6 +65227,16 @@
         <v>11930</v>
       </c>
     </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>11948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1006"/>
+  <dimension ref="A1:Q1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55161,6 +55161,61 @@
         <v>13648</v>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>28603</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>3899</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>7773</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>14415</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>16908</v>
+      </c>
+      <c r="I1007" t="n">
+        <v>18835</v>
+      </c>
+      <c r="J1007" t="n">
+        <v>20412</v>
+      </c>
+      <c r="K1007" t="n">
+        <v>3058</v>
+      </c>
+      <c r="L1007" t="n">
+        <v>901</v>
+      </c>
+      <c r="M1007" t="n">
+        <v>2328</v>
+      </c>
+      <c r="N1007" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1007" t="n">
+        <v>3307</v>
+      </c>
+      <c r="P1007" t="n">
+        <v>7809</v>
+      </c>
+      <c r="Q1007" t="n">
+        <v>13669</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55172,7 +55227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1006"/>
+  <dimension ref="A1:B1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65237,6 +65292,16 @@
         <v>11948</v>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>11958</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1007"/>
+  <dimension ref="A1:Q1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55216,6 +55216,61 @@
         <v>13669</v>
       </c>
     </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>28598</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>3891</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>7772</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>14410</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>16907</v>
+      </c>
+      <c r="I1008" t="n">
+        <v>18841</v>
+      </c>
+      <c r="J1008" t="n">
+        <v>20409</v>
+      </c>
+      <c r="K1008" t="n">
+        <v>3059</v>
+      </c>
+      <c r="L1008" t="n">
+        <v>903</v>
+      </c>
+      <c r="M1008" t="n">
+        <v>2321</v>
+      </c>
+      <c r="N1008" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1008" t="n">
+        <v>3298</v>
+      </c>
+      <c r="P1008" t="n">
+        <v>7800</v>
+      </c>
+      <c r="Q1008" t="n">
+        <v>13672</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55227,7 +55282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1007"/>
+  <dimension ref="A1:B1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65302,6 +65357,16 @@
         <v>11958</v>
       </c>
     </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>11978</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1008"/>
+  <dimension ref="A1:Q1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55271,6 +55271,61 @@
         <v>13672</v>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>28599</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>3892</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>7776</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>11376</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>14421</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>16901</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>18832</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>20403</v>
+      </c>
+      <c r="K1009" t="n">
+        <v>3063</v>
+      </c>
+      <c r="L1009" t="n">
+        <v>907</v>
+      </c>
+      <c r="M1009" t="n">
+        <v>2315</v>
+      </c>
+      <c r="N1009" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1009" t="n">
+        <v>3299</v>
+      </c>
+      <c r="P1009" t="n">
+        <v>7800</v>
+      </c>
+      <c r="Q1009" t="n">
+        <v>13677</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55282,7 +55337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1008"/>
+  <dimension ref="A1:B1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65367,6 +65422,16 @@
         <v>11978</v>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>12000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1009"/>
+  <dimension ref="A1:Q1010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55326,6 +55326,61 @@
         <v>13677</v>
       </c>
     </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>28589</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>3887</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>7765</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>11364</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>14409</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>16889</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>18816</v>
+      </c>
+      <c r="J1010" t="n">
+        <v>20391</v>
+      </c>
+      <c r="K1010" t="n">
+        <v>3066</v>
+      </c>
+      <c r="L1010" t="n">
+        <v>909</v>
+      </c>
+      <c r="M1010" t="n">
+        <v>2313</v>
+      </c>
+      <c r="N1010" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1010" t="n">
+        <v>3300</v>
+      </c>
+      <c r="P1010" t="n">
+        <v>7807</v>
+      </c>
+      <c r="Q1010" t="n">
+        <v>13684</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55337,7 +55392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1009"/>
+  <dimension ref="A1:B1010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65432,6 +65487,16 @@
         <v>12000</v>
       </c>
     </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>12021</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1010"/>
+  <dimension ref="A1:Q1011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55381,6 +55381,61 @@
         <v>13684</v>
       </c>
     </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>28570</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>3886</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>7758</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>11366</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>14400</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>16879</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>18804</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>20373</v>
+      </c>
+      <c r="K1011" t="n">
+        <v>3049</v>
+      </c>
+      <c r="L1011" t="n">
+        <v>911</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>2317</v>
+      </c>
+      <c r="N1011" t="n">
+        <v>348</v>
+      </c>
+      <c r="O1011" t="n">
+        <v>3308</v>
+      </c>
+      <c r="P1011" t="n">
+        <v>7813</v>
+      </c>
+      <c r="Q1011" t="n">
+        <v>13682</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55392,7 +55447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1010"/>
+  <dimension ref="A1:B1011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65497,6 +65552,16 @@
         <v>12021</v>
       </c>
     </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>12018</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1011"/>
+  <dimension ref="A1:Q1012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55436,6 +55436,61 @@
         <v>13682</v>
       </c>
     </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>28575</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>3892</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>7754</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>11351</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>14399</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>16868</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>18798</v>
+      </c>
+      <c r="J1012" t="n">
+        <v>20374</v>
+      </c>
+      <c r="K1012" t="n">
+        <v>3044</v>
+      </c>
+      <c r="L1012" t="n">
+        <v>919</v>
+      </c>
+      <c r="M1012" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N1012" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1012" t="n">
+        <v>3306</v>
+      </c>
+      <c r="P1012" t="n">
+        <v>7811</v>
+      </c>
+      <c r="Q1012" t="n">
+        <v>13689</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55447,7 +55502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1011"/>
+  <dimension ref="A1:B1012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65562,6 +65617,16 @@
         <v>12018</v>
       </c>
     </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>12039</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1012"/>
+  <dimension ref="A1:Q1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55491,6 +55491,61 @@
         <v>13689</v>
       </c>
     </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>28588</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>3884</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>7741</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>11358</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>14409</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>16889</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>18825</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>20401</v>
+      </c>
+      <c r="K1013" t="n">
+        <v>3035</v>
+      </c>
+      <c r="L1013" t="n">
+        <v>921</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>2312</v>
+      </c>
+      <c r="N1013" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1013" t="n">
+        <v>3314</v>
+      </c>
+      <c r="P1013" t="n">
+        <v>7817</v>
+      </c>
+      <c r="Q1013" t="n">
+        <v>13699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55502,7 +55557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1012"/>
+  <dimension ref="A1:B1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65627,6 +65682,16 @@
         <v>12039</v>
       </c>
     </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>12079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1013"/>
+  <dimension ref="A1:Q1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55546,6 +55546,61 @@
         <v>13699</v>
       </c>
     </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>28587</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>3885</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>7744</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>11354</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>14409</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>16894</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>18828</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>20401</v>
+      </c>
+      <c r="K1014" t="n">
+        <v>3045</v>
+      </c>
+      <c r="L1014" t="n">
+        <v>922</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>2301</v>
+      </c>
+      <c r="N1014" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1014" t="n">
+        <v>3316</v>
+      </c>
+      <c r="P1014" t="n">
+        <v>7831</v>
+      </c>
+      <c r="Q1014" t="n">
+        <v>13715</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55557,7 +55612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1013"/>
+  <dimension ref="A1:B1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65692,6 +65747,16 @@
         <v>12079</v>
       </c>
     </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>12081</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1014"/>
+  <dimension ref="A1:Q1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55601,6 +55601,61 @@
         <v>13715</v>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>28585</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>7747</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>11362</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>14426</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>16915</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>18842</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>20414</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>3046</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>915</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>2297</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1015" t="n">
+        <v>3314</v>
+      </c>
+      <c r="P1015" t="n">
+        <v>7829</v>
+      </c>
+      <c r="Q1015" t="n">
+        <v>13720</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55612,7 +55667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1014"/>
+  <dimension ref="A1:B1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65757,6 +65812,16 @@
         <v>12081</v>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>12097</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1015"/>
+  <dimension ref="A1:Q1016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55656,6 +55656,61 @@
         <v>13720</v>
       </c>
     </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>28580</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>3889</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>7755</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>11369</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>14431</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>16904</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>18837</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>20405</v>
+      </c>
+      <c r="K1016" t="n">
+        <v>3051</v>
+      </c>
+      <c r="L1016" t="n">
+        <v>917</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>2296</v>
+      </c>
+      <c r="N1016" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1016" t="n">
+        <v>3318</v>
+      </c>
+      <c r="P1016" t="n">
+        <v>7829</v>
+      </c>
+      <c r="Q1016" t="n">
+        <v>13712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55667,7 +55722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1015"/>
+  <dimension ref="A1:B1016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65822,6 +65877,16 @@
         <v>12097</v>
       </c>
     </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>12066</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1016"/>
+  <dimension ref="A1:Q1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55711,6 +55711,61 @@
         <v>13712</v>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>28583</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>3898</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>7767</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>11380</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>14438</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>16920</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>18851</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>20410</v>
+      </c>
+      <c r="K1017" t="n">
+        <v>3038</v>
+      </c>
+      <c r="L1017" t="n">
+        <v>917</v>
+      </c>
+      <c r="M1017" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N1017" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1017" t="n">
+        <v>3329</v>
+      </c>
+      <c r="P1017" t="n">
+        <v>7846</v>
+      </c>
+      <c r="Q1017" t="n">
+        <v>13737</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55722,7 +55777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1016"/>
+  <dimension ref="A1:B1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65887,6 +65942,16 @@
         <v>12066</v>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>12078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1017"/>
+  <dimension ref="A1:Q1018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55766,6 +55766,61 @@
         <v>13737</v>
       </c>
     </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>28593</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>3904</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>7779</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>11389</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>14446</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>16928</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>18863</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>20412</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>3052</v>
+      </c>
+      <c r="L1018" t="n">
+        <v>916</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>2297</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>342</v>
+      </c>
+      <c r="O1018" t="n">
+        <v>3333</v>
+      </c>
+      <c r="P1018" t="n">
+        <v>7858</v>
+      </c>
+      <c r="Q1018" t="n">
+        <v>13755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55777,7 +55832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1017"/>
+  <dimension ref="A1:B1018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65952,6 +66007,16 @@
         <v>12078</v>
       </c>
     </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>12061</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1018"/>
+  <dimension ref="A1:Q1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55821,6 +55821,61 @@
         <v>13755</v>
       </c>
     </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>28604</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>7772</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>11386</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>14436</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>16926</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>18865</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>20415</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>3069</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>919</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>2291</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>342</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>3325</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>7851</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>13761</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55832,7 +55887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1018"/>
+  <dimension ref="A1:B1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66017,6 +66072,16 @@
         <v>12061</v>
       </c>
     </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>12064</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1019"/>
+  <dimension ref="A1:Q1020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55876,6 +55876,61 @@
         <v>13761</v>
       </c>
     </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>28642</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>3904</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>7786</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>11407</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>14465</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>16957</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>18896</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>20447</v>
+      </c>
+      <c r="K1020" t="n">
+        <v>3077</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>922</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>2294</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>342</v>
+      </c>
+      <c r="O1020" t="n">
+        <v>3328</v>
+      </c>
+      <c r="P1020" t="n">
+        <v>7868</v>
+      </c>
+      <c r="Q1020" t="n">
+        <v>13790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55887,7 +55942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1019"/>
+  <dimension ref="A1:B1020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66082,6 +66137,16 @@
         <v>12064</v>
       </c>
     </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>12085</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1020"/>
+  <dimension ref="A1:Q1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55931,6 +55931,61 @@
         <v>13790</v>
       </c>
     </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>28618</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>3897</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>7776</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>11397</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>14440</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>16931</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>18866</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>20419</v>
+      </c>
+      <c r="K1021" t="n">
+        <v>3077</v>
+      </c>
+      <c r="L1021" t="n">
+        <v>931</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>2290</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1021" t="n">
+        <v>3327</v>
+      </c>
+      <c r="P1021" t="n">
+        <v>7871</v>
+      </c>
+      <c r="Q1021" t="n">
+        <v>13781</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55942,7 +55997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1020"/>
+  <dimension ref="A1:B1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66147,6 +66202,16 @@
         <v>12085</v>
       </c>
     </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>12064</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1021"/>
+  <dimension ref="A1:Q1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55986,6 +55986,61 @@
         <v>13781</v>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>28643</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>3892</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>7773</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>11402</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>14440</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>16933</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>18864</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>20423</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>3096</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>929</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>2288</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>3323</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>7870</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>13792</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55997,7 +56052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1021"/>
+  <dimension ref="A1:B1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66212,6 +66267,16 @@
         <v>12064</v>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>12062</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1022"/>
+  <dimension ref="A1:Q1023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56041,6 +56041,61 @@
         <v>13792</v>
       </c>
     </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>28683</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>3894</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>7787</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>11422</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>14456</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>16965</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>18902</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>20458</v>
+      </c>
+      <c r="K1023" t="n">
+        <v>3101</v>
+      </c>
+      <c r="L1023" t="n">
+        <v>929</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>2284</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1023" t="n">
+        <v>3329</v>
+      </c>
+      <c r="P1023" t="n">
+        <v>7891</v>
+      </c>
+      <c r="Q1023" t="n">
+        <v>13837</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56052,7 +56107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1022"/>
+  <dimension ref="A1:B1023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66277,6 +66332,16 @@
         <v>12062</v>
       </c>
     </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>12076</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1023"/>
+  <dimension ref="A1:Q1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56096,6 +56096,61 @@
         <v>13837</v>
       </c>
     </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>28706</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>3887</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>7774</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>11409</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>14448</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>16974</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>18913</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>20470</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>3117</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>933</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>2284</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>348</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>3335</v>
+      </c>
+      <c r="P1024" t="n">
+        <v>7913</v>
+      </c>
+      <c r="Q1024" t="n">
+        <v>13857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56107,7 +56162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1023"/>
+  <dimension ref="A1:B1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66342,6 +66397,16 @@
         <v>12076</v>
       </c>
     </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>12103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1024"/>
+  <dimension ref="A1:Q1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56151,6 +56151,61 @@
         <v>13857</v>
       </c>
     </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>28731</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>3898</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>7782</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>11427</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>14450</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>16985</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>18928</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>20487</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>3118</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>933</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>2280</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>350</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>3346</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>7928</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>13875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56162,7 +56217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1024"/>
+  <dimension ref="A1:B1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66407,6 +66462,16 @@
         <v>12103</v>
       </c>
     </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>12079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1025"/>
+  <dimension ref="A1:Q1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56206,6 +56206,61 @@
         <v>13875</v>
       </c>
     </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>28764</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>7783</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>11450</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>14481</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>17018</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>18965</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>20520</v>
+      </c>
+      <c r="K1026" t="n">
+        <v>3119</v>
+      </c>
+      <c r="L1026" t="n">
+        <v>937</v>
+      </c>
+      <c r="M1026" t="n">
+        <v>2284</v>
+      </c>
+      <c r="N1026" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1026" t="n">
+        <v>3355</v>
+      </c>
+      <c r="P1026" t="n">
+        <v>7932</v>
+      </c>
+      <c r="Q1026" t="n">
+        <v>13884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56217,7 +56272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1025"/>
+  <dimension ref="A1:B1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66472,6 +66527,16 @@
         <v>12079</v>
       </c>
     </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>12065</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1026"/>
+  <dimension ref="A1:Q1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56261,6 +56261,61 @@
         <v>13884</v>
       </c>
     </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>28821</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>3901</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>7808</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>11488</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>14518</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>17056</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>19012</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>20567</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>3121</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>937</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>2287</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>348</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>3360</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>7952</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>13938</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56272,7 +56327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1026"/>
+  <dimension ref="A1:B1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66537,6 +66592,16 @@
         <v>12065</v>
       </c>
     </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>12105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1027"/>
+  <dimension ref="A1:Q1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56316,6 +56316,61 @@
         <v>13938</v>
       </c>
     </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>28858</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>998</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>7805</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>11488</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>14523</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>17069</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>19032</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>20591</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>3131</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>934</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>2290</v>
+      </c>
+      <c r="N1028" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1028" t="n">
+        <v>3356</v>
+      </c>
+      <c r="P1028" t="n">
+        <v>7959</v>
+      </c>
+      <c r="Q1028" t="n">
+        <v>13947</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56327,7 +56382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1027"/>
+  <dimension ref="A1:B1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66602,6 +66657,16 @@
         <v>12105</v>
       </c>
     </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>12139</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1028"/>
+  <dimension ref="A1:Q1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56371,6 +56371,61 @@
         <v>13947</v>
       </c>
     </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>28918</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>997</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>3905</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>7807</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>11505</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>14551</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>17097</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>19067</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>20627</v>
+      </c>
+      <c r="K1029" t="n">
+        <v>3140</v>
+      </c>
+      <c r="L1029" t="n">
+        <v>927</v>
+      </c>
+      <c r="M1029" t="n">
+        <v>2298</v>
+      </c>
+      <c r="N1029" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1029" t="n">
+        <v>3369</v>
+      </c>
+      <c r="P1029" t="n">
+        <v>7971</v>
+      </c>
+      <c r="Q1029" t="n">
+        <v>13967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56382,7 +56437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1028"/>
+  <dimension ref="A1:B1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66667,6 +66722,16 @@
         <v>12139</v>
       </c>
     </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>12151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1029"/>
+  <dimension ref="A1:Q1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56426,6 +56426,61 @@
         <v>13967</v>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>28942</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>995</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>3922</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>7817</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>11513</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>14577</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>17120</v>
+      </c>
+      <c r="I1030" t="n">
+        <v>19090</v>
+      </c>
+      <c r="J1030" t="n">
+        <v>20654</v>
+      </c>
+      <c r="K1030" t="n">
+        <v>3132</v>
+      </c>
+      <c r="L1030" t="n">
+        <v>930</v>
+      </c>
+      <c r="M1030" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N1030" t="n">
+        <v>348</v>
+      </c>
+      <c r="O1030" t="n">
+        <v>3384</v>
+      </c>
+      <c r="P1030" t="n">
+        <v>7990</v>
+      </c>
+      <c r="Q1030" t="n">
+        <v>13985</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56437,7 +56492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1029"/>
+  <dimension ref="A1:B1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66732,6 +66787,16 @@
         <v>12151</v>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>12192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1030"/>
+  <dimension ref="A1:Q1031"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56481,6 +56481,61 @@
         <v>13985</v>
       </c>
     </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>28945</v>
+      </c>
+      <c r="C1031" t="n">
+        <v>990</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>3922</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>7808</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>11507</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>14582</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>17125</v>
+      </c>
+      <c r="I1031" t="n">
+        <v>19091</v>
+      </c>
+      <c r="J1031" t="n">
+        <v>20653</v>
+      </c>
+      <c r="K1031" t="n">
+        <v>3140</v>
+      </c>
+      <c r="L1031" t="n">
+        <v>924</v>
+      </c>
+      <c r="M1031" t="n">
+        <v>2298</v>
+      </c>
+      <c r="N1031" t="n">
+        <v>350</v>
+      </c>
+      <c r="O1031" t="n">
+        <v>3386</v>
+      </c>
+      <c r="P1031" t="n">
+        <v>7995</v>
+      </c>
+      <c r="Q1031" t="n">
+        <v>13987</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56492,7 +56547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1030"/>
+  <dimension ref="A1:B1031"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66797,6 +66852,16 @@
         <v>12192</v>
       </c>
     </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>12207</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1031"/>
+  <dimension ref="A1:Q1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56536,6 +56536,61 @@
         <v>13987</v>
       </c>
     </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>28921</v>
+      </c>
+      <c r="C1032" t="n">
+        <v>995</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>3919</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>7803</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>11489</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>14560</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>17094</v>
+      </c>
+      <c r="I1032" t="n">
+        <v>19062</v>
+      </c>
+      <c r="J1032" t="n">
+        <v>20627</v>
+      </c>
+      <c r="K1032" t="n">
+        <v>3137</v>
+      </c>
+      <c r="L1032" t="n">
+        <v>924</v>
+      </c>
+      <c r="M1032" t="n">
+        <v>2310</v>
+      </c>
+      <c r="N1032" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1032" t="n">
+        <v>3380</v>
+      </c>
+      <c r="P1032" t="n">
+        <v>7994</v>
+      </c>
+      <c r="Q1032" t="n">
+        <v>13976</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56547,7 +56602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1031"/>
+  <dimension ref="A1:B1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66862,6 +66917,16 @@
         <v>12207</v>
       </c>
     </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>12199</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1032"/>
+  <dimension ref="A1:Q1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56591,6 +56591,61 @@
         <v>13976</v>
       </c>
     </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>28912</v>
+      </c>
+      <c r="C1033" t="n">
+        <v>998</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>3924</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>7804</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>11493</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>14580</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>17111</v>
+      </c>
+      <c r="I1033" t="n">
+        <v>19076</v>
+      </c>
+      <c r="J1033" t="n">
+        <v>20633</v>
+      </c>
+      <c r="K1033" t="n">
+        <v>3135</v>
+      </c>
+      <c r="L1033" t="n">
+        <v>927</v>
+      </c>
+      <c r="M1033" t="n">
+        <v>2304</v>
+      </c>
+      <c r="N1033" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1033" t="n">
+        <v>3378</v>
+      </c>
+      <c r="P1033" t="n">
+        <v>7996</v>
+      </c>
+      <c r="Q1033" t="n">
+        <v>13974</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56602,7 +56657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1032"/>
+  <dimension ref="A1:B1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66927,6 +66982,16 @@
         <v>12199</v>
       </c>
     </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>12124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1033"/>
+  <dimension ref="A1:Q1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56646,6 +56646,61 @@
         <v>13974</v>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>28967</v>
+      </c>
+      <c r="C1034" t="n">
+        <v>996</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>3919</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>7810</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>11502</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>14594</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>17137</v>
+      </c>
+      <c r="I1034" t="n">
+        <v>19108</v>
+      </c>
+      <c r="J1034" t="n">
+        <v>20668</v>
+      </c>
+      <c r="K1034" t="n">
+        <v>3146</v>
+      </c>
+      <c r="L1034" t="n">
+        <v>934</v>
+      </c>
+      <c r="M1034" t="n">
+        <v>2309</v>
+      </c>
+      <c r="N1034" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1034" t="n">
+        <v>3386</v>
+      </c>
+      <c r="P1034" t="n">
+        <v>8009</v>
+      </c>
+      <c r="Q1034" t="n">
+        <v>13992</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56657,7 +56712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1033"/>
+  <dimension ref="A1:B1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66992,6 +67047,16 @@
         <v>12124</v>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>12141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1034"/>
+  <dimension ref="A1:Q1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56701,6 +56701,61 @@
         <v>13992</v>
       </c>
     </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>28968</v>
+      </c>
+      <c r="C1035" t="n">
+        <v>999</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>3920</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>7809</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>11494</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>14580</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>17127</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>19103</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>20666</v>
+      </c>
+      <c r="K1035" t="n">
+        <v>3144</v>
+      </c>
+      <c r="L1035" t="n">
+        <v>941</v>
+      </c>
+      <c r="M1035" t="n">
+        <v>2307</v>
+      </c>
+      <c r="N1035" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1035" t="n">
+        <v>3391</v>
+      </c>
+      <c r="P1035" t="n">
+        <v>8012</v>
+      </c>
+      <c r="Q1035" t="n">
+        <v>14001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56712,7 +56767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1034"/>
+  <dimension ref="A1:B1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67057,6 +67112,16 @@
         <v>12141</v>
       </c>
     </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>12155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1035"/>
+  <dimension ref="A1:Q1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56756,6 +56756,61 @@
         <v>14001</v>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>28982</v>
+      </c>
+      <c r="C1036" t="n">
+        <v>993</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>3917</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>7803</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>11506</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>14587</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>17135</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>19104</v>
+      </c>
+      <c r="J1036" t="n">
+        <v>20677</v>
+      </c>
+      <c r="K1036" t="n">
+        <v>3144</v>
+      </c>
+      <c r="L1036" t="n">
+        <v>940</v>
+      </c>
+      <c r="M1036" t="n">
+        <v>2305</v>
+      </c>
+      <c r="N1036" t="n">
+        <v>343</v>
+      </c>
+      <c r="O1036" t="n">
+        <v>3391</v>
+      </c>
+      <c r="P1036" t="n">
+        <v>8017</v>
+      </c>
+      <c r="Q1036" t="n">
+        <v>14008</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56767,7 +56822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1035"/>
+  <dimension ref="A1:B1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67122,6 +67177,16 @@
         <v>12155</v>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>12132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1036"/>
+  <dimension ref="A1:Q1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56811,6 +56811,61 @@
         <v>14008</v>
       </c>
     </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>29012</v>
+      </c>
+      <c r="C1037" t="n">
+        <v>999</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>3919</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>7814</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>11518</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>14610</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>17159</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>19120</v>
+      </c>
+      <c r="J1037" t="n">
+        <v>20697</v>
+      </c>
+      <c r="K1037" t="n">
+        <v>3150</v>
+      </c>
+      <c r="L1037" t="n">
+        <v>946</v>
+      </c>
+      <c r="M1037" t="n">
+        <v>2307</v>
+      </c>
+      <c r="N1037" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1037" t="n">
+        <v>3395</v>
+      </c>
+      <c r="P1037" t="n">
+        <v>8029</v>
+      </c>
+      <c r="Q1037" t="n">
+        <v>14031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56822,7 +56877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1036"/>
+  <dimension ref="A1:B1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67187,6 +67242,16 @@
         <v>12132</v>
       </c>
     </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>12133</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1037"/>
+  <dimension ref="A1:Q1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56866,6 +56866,61 @@
         <v>14031</v>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>29002</v>
+      </c>
+      <c r="C1038" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>3914</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>7809</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>11518</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>14604</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>17146</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>19106</v>
+      </c>
+      <c r="J1038" t="n">
+        <v>20685</v>
+      </c>
+      <c r="K1038" t="n">
+        <v>3156</v>
+      </c>
+      <c r="L1038" t="n">
+        <v>948</v>
+      </c>
+      <c r="M1038" t="n">
+        <v>2299</v>
+      </c>
+      <c r="N1038" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1038" t="n">
+        <v>3394</v>
+      </c>
+      <c r="P1038" t="n">
+        <v>8031</v>
+      </c>
+      <c r="Q1038" t="n">
+        <v>14031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56877,7 +56932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1037"/>
+  <dimension ref="A1:B1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67252,6 +67307,16 @@
         <v>12133</v>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>12104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1038"/>
+  <dimension ref="A1:Q1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56921,6 +56921,61 @@
         <v>14031</v>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>29046</v>
+      </c>
+      <c r="C1039" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>3915</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>7817</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>11526</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>14626</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>17166</v>
+      </c>
+      <c r="I1039" t="n">
+        <v>19137</v>
+      </c>
+      <c r="J1039" t="n">
+        <v>20721</v>
+      </c>
+      <c r="K1039" t="n">
+        <v>3158</v>
+      </c>
+      <c r="L1039" t="n">
+        <v>954</v>
+      </c>
+      <c r="M1039" t="n">
+        <v>2298</v>
+      </c>
+      <c r="N1039" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1039" t="n">
+        <v>3392</v>
+      </c>
+      <c r="P1039" t="n">
+        <v>8044</v>
+      </c>
+      <c r="Q1039" t="n">
+        <v>14053</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56932,7 +56987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1038"/>
+  <dimension ref="A1:B1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67317,6 +67372,16 @@
         <v>12104</v>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>12088</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1039"/>
+  <dimension ref="A1:Q1040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56976,6 +56976,61 @@
         <v>14053</v>
       </c>
     </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>29065</v>
+      </c>
+      <c r="C1040" t="n">
+        <v>999</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>3909</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>7803</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>11520</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>14630</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>17172</v>
+      </c>
+      <c r="I1040" t="n">
+        <v>19139</v>
+      </c>
+      <c r="J1040" t="n">
+        <v>20726</v>
+      </c>
+      <c r="K1040" t="n">
+        <v>3176</v>
+      </c>
+      <c r="L1040" t="n">
+        <v>946</v>
+      </c>
+      <c r="M1040" t="n">
+        <v>2301</v>
+      </c>
+      <c r="N1040" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1040" t="n">
+        <v>3403</v>
+      </c>
+      <c r="P1040" t="n">
+        <v>8054</v>
+      </c>
+      <c r="Q1040" t="n">
+        <v>14070</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56987,7 +57042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1039"/>
+  <dimension ref="A1:B1040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67382,6 +67437,16 @@
         <v>12088</v>
       </c>
     </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>12108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1040"/>
+  <dimension ref="A1:Q1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57031,6 +57031,61 @@
         <v>14070</v>
       </c>
     </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>29119</v>
+      </c>
+      <c r="C1041" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>3922</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>7818</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>11526</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>14651</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>17187</v>
+      </c>
+      <c r="I1041" t="n">
+        <v>19164</v>
+      </c>
+      <c r="J1041" t="n">
+        <v>20754</v>
+      </c>
+      <c r="K1041" t="n">
+        <v>3176</v>
+      </c>
+      <c r="L1041" t="n">
+        <v>944</v>
+      </c>
+      <c r="M1041" t="n">
+        <v>2315</v>
+      </c>
+      <c r="N1041" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1041" t="n">
+        <v>3404</v>
+      </c>
+      <c r="P1041" t="n">
+        <v>8075</v>
+      </c>
+      <c r="Q1041" t="n">
+        <v>14096</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57042,7 +57097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1040"/>
+  <dimension ref="A1:B1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67447,6 +67502,16 @@
         <v>12108</v>
       </c>
     </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>12172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1041"/>
+  <dimension ref="A1:Q1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57086,6 +57086,61 @@
         <v>14096</v>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>29172</v>
+      </c>
+      <c r="C1042" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>3918</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>7840</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>11538</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>14665</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>17206</v>
+      </c>
+      <c r="I1042" t="n">
+        <v>19189</v>
+      </c>
+      <c r="J1042" t="n">
+        <v>20793</v>
+      </c>
+      <c r="K1042" t="n">
+        <v>3187</v>
+      </c>
+      <c r="L1042" t="n">
+        <v>943</v>
+      </c>
+      <c r="M1042" t="n">
+        <v>2317</v>
+      </c>
+      <c r="N1042" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1042" t="n">
+        <v>3409</v>
+      </c>
+      <c r="P1042" t="n">
+        <v>8101</v>
+      </c>
+      <c r="Q1042" t="n">
+        <v>14138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57097,7 +57152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1041"/>
+  <dimension ref="A1:B1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67512,6 +67567,16 @@
         <v>12172</v>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>12183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1042"/>
+  <dimension ref="A1:Q1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57141,6 +57141,61 @@
         <v>14138</v>
       </c>
     </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>29175</v>
+      </c>
+      <c r="C1043" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>3919</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>7844</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>11532</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>14655</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>17204</v>
+      </c>
+      <c r="I1043" t="n">
+        <v>19189</v>
+      </c>
+      <c r="J1043" t="n">
+        <v>20795</v>
+      </c>
+      <c r="K1043" t="n">
+        <v>3192</v>
+      </c>
+      <c r="L1043" t="n">
+        <v>945</v>
+      </c>
+      <c r="M1043" t="n">
+        <v>2322</v>
+      </c>
+      <c r="N1043" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1043" t="n">
+        <v>3421</v>
+      </c>
+      <c r="P1043" t="n">
+        <v>8105</v>
+      </c>
+      <c r="Q1043" t="n">
+        <v>14144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57152,7 +57207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1042"/>
+  <dimension ref="A1:B1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67577,6 +67632,16 @@
         <v>12183</v>
       </c>
     </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>12153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1043"/>
+  <dimension ref="A1:Q1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57196,6 +57196,61 @@
         <v>14144</v>
       </c>
     </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>29190</v>
+      </c>
+      <c r="C1044" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>3915</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>7846</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>11538</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>14654</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>17205</v>
+      </c>
+      <c r="I1044" t="n">
+        <v>19188</v>
+      </c>
+      <c r="J1044" t="n">
+        <v>20799</v>
+      </c>
+      <c r="K1044" t="n">
+        <v>3194</v>
+      </c>
+      <c r="L1044" t="n">
+        <v>951</v>
+      </c>
+      <c r="M1044" t="n">
+        <v>2322</v>
+      </c>
+      <c r="N1044" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1044" t="n">
+        <v>3426</v>
+      </c>
+      <c r="P1044" t="n">
+        <v>8111</v>
+      </c>
+      <c r="Q1044" t="n">
+        <v>14150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57207,7 +57262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1043"/>
+  <dimension ref="A1:B1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67642,6 +67697,16 @@
         <v>12153</v>
       </c>
     </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>12176</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1044"/>
+  <dimension ref="A1:Q1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57251,6 +57251,61 @@
         <v>14150</v>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>29222</v>
+      </c>
+      <c r="C1045" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>7826</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>11531</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>14648</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>17203</v>
+      </c>
+      <c r="I1045" t="n">
+        <v>19189</v>
+      </c>
+      <c r="J1045" t="n">
+        <v>20806</v>
+      </c>
+      <c r="K1045" t="n">
+        <v>3209</v>
+      </c>
+      <c r="L1045" t="n">
+        <v>947</v>
+      </c>
+      <c r="M1045" t="n">
+        <v>2326</v>
+      </c>
+      <c r="N1045" t="n">
+        <v>348</v>
+      </c>
+      <c r="O1045" t="n">
+        <v>3428</v>
+      </c>
+      <c r="P1045" t="n">
+        <v>8122</v>
+      </c>
+      <c r="Q1045" t="n">
+        <v>14169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57262,7 +57317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1044"/>
+  <dimension ref="A1:B1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67707,6 +67762,16 @@
         <v>12176</v>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>12200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1045"/>
+  <dimension ref="A1:Q1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57306,6 +57306,61 @@
         <v>14169</v>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>29155</v>
+      </c>
+      <c r="C1046" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>3901</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>7795</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>11493</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>14595</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>17145</v>
+      </c>
+      <c r="I1046" t="n">
+        <v>19140</v>
+      </c>
+      <c r="J1046" t="n">
+        <v>20738</v>
+      </c>
+      <c r="K1046" t="n">
+        <v>3206</v>
+      </c>
+      <c r="L1046" t="n">
+        <v>950</v>
+      </c>
+      <c r="M1046" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N1046" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1046" t="n">
+        <v>3427</v>
+      </c>
+      <c r="P1046" t="n">
+        <v>8114</v>
+      </c>
+      <c r="Q1046" t="n">
+        <v>14134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57317,7 +57372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1045"/>
+  <dimension ref="A1:B1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67772,6 +67827,16 @@
         <v>12200</v>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>12154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1046"/>
+  <dimension ref="A1:Q1047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57361,6 +57361,61 @@
         <v>14134</v>
       </c>
     </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>29172</v>
+      </c>
+      <c r="C1047" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>3906</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>7792</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>11497</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>14607</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>17157</v>
+      </c>
+      <c r="I1047" t="n">
+        <v>19157</v>
+      </c>
+      <c r="J1047" t="n">
+        <v>20747</v>
+      </c>
+      <c r="K1047" t="n">
+        <v>3214</v>
+      </c>
+      <c r="L1047" t="n">
+        <v>956</v>
+      </c>
+      <c r="M1047" t="n">
+        <v>2315</v>
+      </c>
+      <c r="N1047" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1047" t="n">
+        <v>3429</v>
+      </c>
+      <c r="P1047" t="n">
+        <v>8124</v>
+      </c>
+      <c r="Q1047" t="n">
+        <v>14157</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57372,7 +57427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1046"/>
+  <dimension ref="A1:B1047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67837,6 +67892,16 @@
         <v>12154</v>
       </c>
     </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>12141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1047"/>
+  <dimension ref="A1:Q1048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57416,6 +57416,61 @@
         <v>14157</v>
       </c>
     </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>29227</v>
+      </c>
+      <c r="C1048" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>3910</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>7812</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>11528</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>14644</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>17199</v>
+      </c>
+      <c r="I1048" t="n">
+        <v>19210</v>
+      </c>
+      <c r="J1048" t="n">
+        <v>20803</v>
+      </c>
+      <c r="K1048" t="n">
+        <v>3217</v>
+      </c>
+      <c r="L1048" t="n">
+        <v>952</v>
+      </c>
+      <c r="M1048" t="n">
+        <v>2319</v>
+      </c>
+      <c r="N1048" t="n">
+        <v>345</v>
+      </c>
+      <c r="O1048" t="n">
+        <v>3435</v>
+      </c>
+      <c r="P1048" t="n">
+        <v>8143</v>
+      </c>
+      <c r="Q1048" t="n">
+        <v>14198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57427,7 +57482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1047"/>
+  <dimension ref="A1:B1048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67902,6 +67957,16 @@
         <v>12141</v>
       </c>
     </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>12153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1048"/>
+  <dimension ref="A1:Q1049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57471,6 +57471,61 @@
         <v>14198</v>
       </c>
     </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>29226</v>
+      </c>
+      <c r="C1049" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>3897</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>7794</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>11518</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>14631</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>17193</v>
+      </c>
+      <c r="I1049" t="n">
+        <v>19208</v>
+      </c>
+      <c r="J1049" t="n">
+        <v>20802</v>
+      </c>
+      <c r="K1049" t="n">
+        <v>3212</v>
+      </c>
+      <c r="L1049" t="n">
+        <v>953</v>
+      </c>
+      <c r="M1049" t="n">
+        <v>2319</v>
+      </c>
+      <c r="N1049" t="n">
+        <v>344</v>
+      </c>
+      <c r="O1049" t="n">
+        <v>3425</v>
+      </c>
+      <c r="P1049" t="n">
+        <v>8133</v>
+      </c>
+      <c r="Q1049" t="n">
+        <v>14197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57482,7 +57537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1048"/>
+  <dimension ref="A1:B1049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67967,6 +68022,16 @@
         <v>12153</v>
       </c>
     </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>12145</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1049"/>
+  <dimension ref="A1:Q1050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57526,6 +57526,61 @@
         <v>14197</v>
       </c>
     </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>29242</v>
+      </c>
+      <c r="C1050" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>3897</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>7797</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>11520</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>14637</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>17207</v>
+      </c>
+      <c r="I1050" t="n">
+        <v>19219</v>
+      </c>
+      <c r="J1050" t="n">
+        <v>20809</v>
+      </c>
+      <c r="K1050" t="n">
+        <v>3225</v>
+      </c>
+      <c r="L1050" t="n">
+        <v>954</v>
+      </c>
+      <c r="M1050" t="n">
+        <v>2322</v>
+      </c>
+      <c r="N1050" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1050" t="n">
+        <v>3434</v>
+      </c>
+      <c r="P1050" t="n">
+        <v>8139</v>
+      </c>
+      <c r="Q1050" t="n">
+        <v>14201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57537,7 +57592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1049"/>
+  <dimension ref="A1:B1050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68032,6 +68087,16 @@
         <v>12145</v>
       </c>
     </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>12197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1050"/>
+  <dimension ref="A1:Q1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57581,6 +57581,61 @@
         <v>14201</v>
       </c>
     </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>29294</v>
+      </c>
+      <c r="C1051" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>3894</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>7802</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>11530</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>14660</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>17240</v>
+      </c>
+      <c r="I1051" t="n">
+        <v>19266</v>
+      </c>
+      <c r="J1051" t="n">
+        <v>20863</v>
+      </c>
+      <c r="K1051" t="n">
+        <v>3229</v>
+      </c>
+      <c r="L1051" t="n">
+        <v>948</v>
+      </c>
+      <c r="M1051" t="n">
+        <v>2323</v>
+      </c>
+      <c r="N1051" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1051" t="n">
+        <v>3442</v>
+      </c>
+      <c r="P1051" t="n">
+        <v>8161</v>
+      </c>
+      <c r="Q1051" t="n">
+        <v>14232</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57592,7 +57647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1050"/>
+  <dimension ref="A1:B1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68097,6 +68152,16 @@
         <v>12197</v>
       </c>
     </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>12196</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1051"/>
+  <dimension ref="A1:Q1052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57636,6 +57636,61 @@
         <v>14232</v>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>29315</v>
+      </c>
+      <c r="C1052" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>3886</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>7802</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>11539</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>14663</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>17247</v>
+      </c>
+      <c r="I1052" t="n">
+        <v>19277</v>
+      </c>
+      <c r="J1052" t="n">
+        <v>20874</v>
+      </c>
+      <c r="K1052" t="n">
+        <v>3229</v>
+      </c>
+      <c r="L1052" t="n">
+        <v>948</v>
+      </c>
+      <c r="M1052" t="n">
+        <v>2327</v>
+      </c>
+      <c r="N1052" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1052" t="n">
+        <v>3441</v>
+      </c>
+      <c r="P1052" t="n">
+        <v>8182</v>
+      </c>
+      <c r="Q1052" t="n">
+        <v>14248</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57647,7 +57702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1051"/>
+  <dimension ref="A1:B1052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68162,6 +68217,16 @@
         <v>12196</v>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>12200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1052"/>
+  <dimension ref="A1:Q1053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57691,6 +57691,61 @@
         <v>14248</v>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>29400</v>
+      </c>
+      <c r="C1053" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>3895</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>7825</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>11563</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>14696</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>17275</v>
+      </c>
+      <c r="I1053" t="n">
+        <v>19326</v>
+      </c>
+      <c r="J1053" t="n">
+        <v>20932</v>
+      </c>
+      <c r="K1053" t="n">
+        <v>3236</v>
+      </c>
+      <c r="L1053" t="n">
+        <v>954</v>
+      </c>
+      <c r="M1053" t="n">
+        <v>2338</v>
+      </c>
+      <c r="N1053" t="n">
+        <v>347</v>
+      </c>
+      <c r="O1053" t="n">
+        <v>3458</v>
+      </c>
+      <c r="P1053" t="n">
+        <v>8206</v>
+      </c>
+      <c r="Q1053" t="n">
+        <v>14291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57702,7 +57757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1052"/>
+  <dimension ref="A1:B1053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68227,6 +68282,16 @@
         <v>12200</v>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>12264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1053"/>
+  <dimension ref="A1:Q1054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57746,6 +57746,61 @@
         <v>14291</v>
       </c>
     </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>29399</v>
+      </c>
+      <c r="C1054" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>3895</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>7811</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>11554</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>14690</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>17264</v>
+      </c>
+      <c r="I1054" t="n">
+        <v>19314</v>
+      </c>
+      <c r="J1054" t="n">
+        <v>20920</v>
+      </c>
+      <c r="K1054" t="n">
+        <v>3236</v>
+      </c>
+      <c r="L1054" t="n">
+        <v>956</v>
+      </c>
+      <c r="M1054" t="n">
+        <v>2344</v>
+      </c>
+      <c r="N1054" t="n">
+        <v>346</v>
+      </c>
+      <c r="O1054" t="n">
+        <v>3469</v>
+      </c>
+      <c r="P1054" t="n">
+        <v>8215</v>
+      </c>
+      <c r="Q1054" t="n">
+        <v>14271</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57757,7 +57812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1053"/>
+  <dimension ref="A1:B1054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68292,6 +68347,16 @@
         <v>12264</v>
       </c>
     </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>12247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1054"/>
+  <dimension ref="A1:Q1055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57801,6 +57801,61 @@
         <v>14271</v>
       </c>
     </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>29470</v>
+      </c>
+      <c r="C1055" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>3896</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>7826</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>11574</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>14718</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>17297</v>
+      </c>
+      <c r="I1055" t="n">
+        <v>19374</v>
+      </c>
+      <c r="J1055" t="n">
+        <v>20977</v>
+      </c>
+      <c r="K1055" t="n">
+        <v>3237</v>
+      </c>
+      <c r="L1055" t="n">
+        <v>959</v>
+      </c>
+      <c r="M1055" t="n">
+        <v>2345</v>
+      </c>
+      <c r="N1055" t="n">
+        <v>350</v>
+      </c>
+      <c r="O1055" t="n">
+        <v>3477</v>
+      </c>
+      <c r="P1055" t="n">
+        <v>8247</v>
+      </c>
+      <c r="Q1055" t="n">
+        <v>14315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57812,7 +57867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1054"/>
+  <dimension ref="A1:B1055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68357,6 +68412,16 @@
         <v>12247</v>
       </c>
     </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>12299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1055"/>
+  <dimension ref="A1:Q1056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57856,6 +57856,61 @@
         <v>14315</v>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>29524</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>3892</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>7840</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>11599</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>14753</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>17343</v>
+      </c>
+      <c r="I1056" t="n">
+        <v>19421</v>
+      </c>
+      <c r="J1056" t="n">
+        <v>21035</v>
+      </c>
+      <c r="K1056" t="n">
+        <v>3239</v>
+      </c>
+      <c r="L1056" t="n">
+        <v>965</v>
+      </c>
+      <c r="M1056" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N1056" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1056" t="n">
+        <v>3488</v>
+      </c>
+      <c r="P1056" t="n">
+        <v>8274</v>
+      </c>
+      <c r="Q1056" t="n">
+        <v>14363</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57867,7 +57922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1055"/>
+  <dimension ref="A1:B1056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68422,6 +68477,16 @@
         <v>12299</v>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>12319</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1056"/>
+  <dimension ref="A1:Q1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57911,6 +57911,61 @@
         <v>14363</v>
       </c>
     </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>29543</v>
+      </c>
+      <c r="C1057" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>3886</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>7829</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>11597</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>14744</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>17346</v>
+      </c>
+      <c r="I1057" t="n">
+        <v>19430</v>
+      </c>
+      <c r="J1057" t="n">
+        <v>21040</v>
+      </c>
+      <c r="K1057" t="n">
+        <v>3242</v>
+      </c>
+      <c r="L1057" t="n">
+        <v>962</v>
+      </c>
+      <c r="M1057" t="n">
+        <v>2355</v>
+      </c>
+      <c r="N1057" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1057" t="n">
+        <v>3492</v>
+      </c>
+      <c r="P1057" t="n">
+        <v>8275</v>
+      </c>
+      <c r="Q1057" t="n">
+        <v>14352</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57922,7 +57977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1056"/>
+  <dimension ref="A1:B1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68487,6 +68542,16 @@
         <v>12319</v>
       </c>
     </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>12328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1057"/>
+  <dimension ref="A1:Q1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57966,6 +57966,61 @@
         <v>14352</v>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>29583</v>
+      </c>
+      <c r="C1058" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>3884</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>7832</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>11614</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>14756</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>17365</v>
+      </c>
+      <c r="I1058" t="n">
+        <v>19450</v>
+      </c>
+      <c r="J1058" t="n">
+        <v>21067</v>
+      </c>
+      <c r="K1058" t="n">
+        <v>3256</v>
+      </c>
+      <c r="L1058" t="n">
+        <v>955</v>
+      </c>
+      <c r="M1058" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N1058" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1058" t="n">
+        <v>3497</v>
+      </c>
+      <c r="P1058" t="n">
+        <v>8284</v>
+      </c>
+      <c r="Q1058" t="n">
+        <v>14380</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57977,7 +58032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1057"/>
+  <dimension ref="A1:B1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68552,6 +68607,16 @@
         <v>12328</v>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>12338</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1058"/>
+  <dimension ref="A1:Q1059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58021,6 +58021,61 @@
         <v>14380</v>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>29635</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>3889</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>7836</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>11623</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>14779</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>17401</v>
+      </c>
+      <c r="I1059" t="n">
+        <v>19495</v>
+      </c>
+      <c r="J1059" t="n">
+        <v>21110</v>
+      </c>
+      <c r="K1059" t="n">
+        <v>3252</v>
+      </c>
+      <c r="L1059" t="n">
+        <v>952</v>
+      </c>
+      <c r="M1059" t="n">
+        <v>2358</v>
+      </c>
+      <c r="N1059" t="n">
+        <v>349</v>
+      </c>
+      <c r="O1059" t="n">
+        <v>3510</v>
+      </c>
+      <c r="P1059" t="n">
+        <v>8309</v>
+      </c>
+      <c r="Q1059" t="n">
+        <v>14421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58032,7 +58087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1058"/>
+  <dimension ref="A1:B1059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68617,6 +68672,16 @@
         <v>12338</v>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>12261</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1059"/>
+  <dimension ref="A1:Q1060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58076,6 +58076,61 @@
         <v>14421</v>
       </c>
     </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>29725</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>3896</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>7851</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>11649</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>14814</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>17449</v>
+      </c>
+      <c r="I1060" t="n">
+        <v>19542</v>
+      </c>
+      <c r="J1060" t="n">
+        <v>21160</v>
+      </c>
+      <c r="K1060" t="n">
+        <v>3262</v>
+      </c>
+      <c r="L1060" t="n">
+        <v>957</v>
+      </c>
+      <c r="M1060" t="n">
+        <v>2370</v>
+      </c>
+      <c r="N1060" t="n">
+        <v>350</v>
+      </c>
+      <c r="O1060" t="n">
+        <v>3515</v>
+      </c>
+      <c r="P1060" t="n">
+        <v>8333</v>
+      </c>
+      <c r="Q1060" t="n">
+        <v>14461</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58087,7 +58142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1059"/>
+  <dimension ref="A1:B1060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68682,6 +68737,16 @@
         <v>12261</v>
       </c>
     </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>12253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1060"/>
+  <dimension ref="A1:Q1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58131,6 +58131,61 @@
         <v>14461</v>
       </c>
     </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>29776</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>3910</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>7871</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>11677</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>14844</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>17501</v>
+      </c>
+      <c r="I1061" t="n">
+        <v>19592</v>
+      </c>
+      <c r="J1061" t="n">
+        <v>21212</v>
+      </c>
+      <c r="K1061" t="n">
+        <v>3268</v>
+      </c>
+      <c r="L1061" t="n">
+        <v>962</v>
+      </c>
+      <c r="M1061" t="n">
+        <v>2376</v>
+      </c>
+      <c r="N1061" t="n">
+        <v>350</v>
+      </c>
+      <c r="O1061" t="n">
+        <v>3534</v>
+      </c>
+      <c r="P1061" t="n">
+        <v>8361</v>
+      </c>
+      <c r="Q1061" t="n">
+        <v>14492</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58142,7 +58197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1060"/>
+  <dimension ref="A1:B1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68747,6 +68802,16 @@
         <v>12253</v>
       </c>
     </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>12263</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1061"/>
+  <dimension ref="A1:Q1062"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58186,6 +58186,61 @@
         <v>14492</v>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>29798</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>3909</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>7878</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>11683</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>14853</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>17501</v>
+      </c>
+      <c r="I1062" t="n">
+        <v>19596</v>
+      </c>
+      <c r="J1062" t="n">
+        <v>21223</v>
+      </c>
+      <c r="K1062" t="n">
+        <v>3267</v>
+      </c>
+      <c r="L1062" t="n">
+        <v>964</v>
+      </c>
+      <c r="M1062" t="n">
+        <v>2377</v>
+      </c>
+      <c r="N1062" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1062" t="n">
+        <v>3550</v>
+      </c>
+      <c r="P1062" t="n">
+        <v>8388</v>
+      </c>
+      <c r="Q1062" t="n">
+        <v>14506</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58197,7 +58252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1061"/>
+  <dimension ref="A1:B1062"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68812,6 +68867,16 @@
         <v>12263</v>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>12203</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1062"/>
+  <dimension ref="A1:Q1063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58241,6 +58241,61 @@
         <v>14506</v>
       </c>
     </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>29851</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>3899</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>7877</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>11688</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>14862</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>17523</v>
+      </c>
+      <c r="I1063" t="n">
+        <v>19624</v>
+      </c>
+      <c r="J1063" t="n">
+        <v>21249</v>
+      </c>
+      <c r="K1063" t="n">
+        <v>3284</v>
+      </c>
+      <c r="L1063" t="n">
+        <v>971</v>
+      </c>
+      <c r="M1063" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N1063" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1063" t="n">
+        <v>3541</v>
+      </c>
+      <c r="P1063" t="n">
+        <v>8392</v>
+      </c>
+      <c r="Q1063" t="n">
+        <v>14526</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58252,7 +58307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1062"/>
+  <dimension ref="A1:B1063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68877,6 +68932,16 @@
         <v>12203</v>
       </c>
     </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>12179</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1063"/>
+  <dimension ref="A1:Q1064"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58296,6 +58296,61 @@
         <v>14526</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>29850</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>3892</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>7867</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>11682</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>14852</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>17506</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>19607</v>
+      </c>
+      <c r="J1064" t="n">
+        <v>21233</v>
+      </c>
+      <c r="K1064" t="n">
+        <v>3288</v>
+      </c>
+      <c r="L1064" t="n">
+        <v>971</v>
+      </c>
+      <c r="M1064" t="n">
+        <v>2387</v>
+      </c>
+      <c r="N1064" t="n">
+        <v>352</v>
+      </c>
+      <c r="O1064" t="n">
+        <v>3535</v>
+      </c>
+      <c r="P1064" t="n">
+        <v>8387</v>
+      </c>
+      <c r="Q1064" t="n">
+        <v>14521</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58307,7 +58362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1063"/>
+  <dimension ref="A1:B1064"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68942,6 +68997,16 @@
         <v>12179</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>12191</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1064"/>
+  <dimension ref="A1:Q1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58351,6 +58351,61 @@
         <v>14521</v>
       </c>
     </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>29925</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>3915</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>7904</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>11733</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>14922</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>17569</v>
+      </c>
+      <c r="I1065" t="n">
+        <v>19675</v>
+      </c>
+      <c r="J1065" t="n">
+        <v>21304</v>
+      </c>
+      <c r="K1065" t="n">
+        <v>3291</v>
+      </c>
+      <c r="L1065" t="n">
+        <v>968</v>
+      </c>
+      <c r="M1065" t="n">
+        <v>2391</v>
+      </c>
+      <c r="N1065" t="n">
+        <v>354</v>
+      </c>
+      <c r="O1065" t="n">
+        <v>3554</v>
+      </c>
+      <c r="P1065" t="n">
+        <v>8424</v>
+      </c>
+      <c r="Q1065" t="n">
+        <v>14581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58362,7 +58417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1064"/>
+  <dimension ref="A1:B1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69007,6 +69062,16 @@
         <v>12191</v>
       </c>
     </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>12193</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1065"/>
+  <dimension ref="A1:Q1066"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58406,6 +58406,61 @@
         <v>14581</v>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>29959</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>3906</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>7886</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>11717</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>14926</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>17579</v>
+      </c>
+      <c r="I1066" t="n">
+        <v>19693</v>
+      </c>
+      <c r="J1066" t="n">
+        <v>21328</v>
+      </c>
+      <c r="K1066" t="n">
+        <v>3301</v>
+      </c>
+      <c r="L1066" t="n">
+        <v>968</v>
+      </c>
+      <c r="M1066" t="n">
+        <v>2389</v>
+      </c>
+      <c r="N1066" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1066" t="n">
+        <v>3562</v>
+      </c>
+      <c r="P1066" t="n">
+        <v>8438</v>
+      </c>
+      <c r="Q1066" t="n">
+        <v>14597</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58417,7 +58472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1065"/>
+  <dimension ref="A1:B1066"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69072,6 +69127,16 @@
         <v>12193</v>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>12214</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1066"/>
+  <dimension ref="A1:Q1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58461,6 +58461,61 @@
         <v>14597</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>29979</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>996</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>3909</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>7873</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>11721</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>14934</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>17593</v>
+      </c>
+      <c r="I1067" t="n">
+        <v>19706</v>
+      </c>
+      <c r="J1067" t="n">
+        <v>21340</v>
+      </c>
+      <c r="K1067" t="n">
+        <v>3310</v>
+      </c>
+      <c r="L1067" t="n">
+        <v>969</v>
+      </c>
+      <c r="M1067" t="n">
+        <v>2390</v>
+      </c>
+      <c r="N1067" t="n">
+        <v>350</v>
+      </c>
+      <c r="O1067" t="n">
+        <v>3558</v>
+      </c>
+      <c r="P1067" t="n">
+        <v>8437</v>
+      </c>
+      <c r="Q1067" t="n">
+        <v>14597</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58472,7 +58527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1066"/>
+  <dimension ref="A1:B1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69137,6 +69192,16 @@
         <v>12214</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>12187</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1067"/>
+  <dimension ref="A1:Q1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58516,6 +58516,61 @@
         <v>14597</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>30032</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>999</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>3909</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>7893</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>11762</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>14980</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>17638</v>
+      </c>
+      <c r="I1068" t="n">
+        <v>19757</v>
+      </c>
+      <c r="J1068" t="n">
+        <v>21395</v>
+      </c>
+      <c r="K1068" t="n">
+        <v>3316</v>
+      </c>
+      <c r="L1068" t="n">
+        <v>968</v>
+      </c>
+      <c r="M1068" t="n">
+        <v>2389</v>
+      </c>
+      <c r="N1068" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1068" t="n">
+        <v>3570</v>
+      </c>
+      <c r="P1068" t="n">
+        <v>8465</v>
+      </c>
+      <c r="Q1068" t="n">
+        <v>14636</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58527,7 +58582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1067"/>
+  <dimension ref="A1:B1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69202,6 +69257,16 @@
         <v>12187</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>12122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1068"/>
+  <dimension ref="A1:Q1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58571,6 +58571,61 @@
         <v>14636</v>
       </c>
     </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>30090</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>3922</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>7903</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>11778</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>15002</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>17659</v>
+      </c>
+      <c r="I1069" t="n">
+        <v>19789</v>
+      </c>
+      <c r="J1069" t="n">
+        <v>21437</v>
+      </c>
+      <c r="K1069" t="n">
+        <v>3321</v>
+      </c>
+      <c r="L1069" t="n">
+        <v>970</v>
+      </c>
+      <c r="M1069" t="n">
+        <v>2396</v>
+      </c>
+      <c r="N1069" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1069" t="n">
+        <v>3578</v>
+      </c>
+      <c r="P1069" t="n">
+        <v>8489</v>
+      </c>
+      <c r="Q1069" t="n">
+        <v>14668</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58582,7 +58637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1068"/>
+  <dimension ref="A1:B1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69267,6 +69322,16 @@
         <v>12122</v>
       </c>
     </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>12013</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1069"/>
+  <dimension ref="A1:Q1070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58626,6 +58626,61 @@
         <v>14668</v>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>30095</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>3929</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>7893</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>11767</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>14986</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>17645</v>
+      </c>
+      <c r="I1070" t="n">
+        <v>19776</v>
+      </c>
+      <c r="J1070" t="n">
+        <v>21424</v>
+      </c>
+      <c r="K1070" t="n">
+        <v>3333</v>
+      </c>
+      <c r="L1070" t="n">
+        <v>972</v>
+      </c>
+      <c r="M1070" t="n">
+        <v>2403</v>
+      </c>
+      <c r="N1070" t="n">
+        <v>352</v>
+      </c>
+      <c r="O1070" t="n">
+        <v>3582</v>
+      </c>
+      <c r="P1070" t="n">
+        <v>8499</v>
+      </c>
+      <c r="Q1070" t="n">
+        <v>14673</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58637,7 +58692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1069"/>
+  <dimension ref="A1:B1070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69332,6 +69387,16 @@
         <v>12013</v>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>11979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1070"/>
+  <dimension ref="A1:Q1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58681,6 +58681,61 @@
         <v>14673</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>30106</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>3926</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>7886</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>11763</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>14980</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>17642</v>
+      </c>
+      <c r="I1071" t="n">
+        <v>19779</v>
+      </c>
+      <c r="J1071" t="n">
+        <v>21434</v>
+      </c>
+      <c r="K1071" t="n">
+        <v>3332</v>
+      </c>
+      <c r="L1071" t="n">
+        <v>970</v>
+      </c>
+      <c r="M1071" t="n">
+        <v>2403</v>
+      </c>
+      <c r="N1071" t="n">
+        <v>355</v>
+      </c>
+      <c r="O1071" t="n">
+        <v>3583</v>
+      </c>
+      <c r="P1071" t="n">
+        <v>8505</v>
+      </c>
+      <c r="Q1071" t="n">
+        <v>14691</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58692,7 +58747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1070"/>
+  <dimension ref="A1:B1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69397,6 +69452,16 @@
         <v>11979</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>11911</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1071"/>
+  <dimension ref="A1:Q1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58736,6 +58736,61 @@
         <v>14691</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>30080</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>3930</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>7882</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>11754</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>14958</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>17608</v>
+      </c>
+      <c r="I1072" t="n">
+        <v>19750</v>
+      </c>
+      <c r="J1072" t="n">
+        <v>21399</v>
+      </c>
+      <c r="K1072" t="n">
+        <v>3328</v>
+      </c>
+      <c r="L1072" t="n">
+        <v>974</v>
+      </c>
+      <c r="M1072" t="n">
+        <v>2412</v>
+      </c>
+      <c r="N1072" t="n">
+        <v>355</v>
+      </c>
+      <c r="O1072" t="n">
+        <v>3590</v>
+      </c>
+      <c r="P1072" t="n">
+        <v>8508</v>
+      </c>
+      <c r="Q1072" t="n">
+        <v>14681</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58747,7 +58802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1071"/>
+  <dimension ref="A1:B1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69462,6 +69517,16 @@
         <v>11911</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>11881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1072"/>
+  <dimension ref="A1:Q1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58791,6 +58791,61 @@
         <v>14681</v>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>30067</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>3929</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>7883</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>11747</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>14947</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>17607</v>
+      </c>
+      <c r="I1073" t="n">
+        <v>19740</v>
+      </c>
+      <c r="J1073" t="n">
+        <v>21392</v>
+      </c>
+      <c r="K1073" t="n">
+        <v>3318</v>
+      </c>
+      <c r="L1073" t="n">
+        <v>979</v>
+      </c>
+      <c r="M1073" t="n">
+        <v>2409</v>
+      </c>
+      <c r="N1073" t="n">
+        <v>355</v>
+      </c>
+      <c r="O1073" t="n">
+        <v>3592</v>
+      </c>
+      <c r="P1073" t="n">
+        <v>8514</v>
+      </c>
+      <c r="Q1073" t="n">
+        <v>14688</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58802,7 +58857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1072"/>
+  <dimension ref="A1:B1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69527,6 +69582,16 @@
         <v>11881</v>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>11853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1073"/>
+  <dimension ref="A1:Q1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58846,6 +58846,61 @@
         <v>14688</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>30048</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>3937</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>7892</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>11759</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>14960</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>17612</v>
+      </c>
+      <c r="I1074" t="n">
+        <v>19741</v>
+      </c>
+      <c r="J1074" t="n">
+        <v>21397</v>
+      </c>
+      <c r="K1074" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L1074" t="n">
+        <v>981</v>
+      </c>
+      <c r="M1074" t="n">
+        <v>2399</v>
+      </c>
+      <c r="N1074" t="n">
+        <v>351</v>
+      </c>
+      <c r="O1074" t="n">
+        <v>3597</v>
+      </c>
+      <c r="P1074" t="n">
+        <v>8519</v>
+      </c>
+      <c r="Q1074" t="n">
+        <v>14697</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58857,7 +58912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1073"/>
+  <dimension ref="A1:B1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69592,6 +69647,16 @@
         <v>11853</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>11741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1074"/>
+  <dimension ref="A1:Q1075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58901,6 +58901,61 @@
         <v>14697</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>30126</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>3940</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>7905</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>11779</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>14993</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>17667</v>
+      </c>
+      <c r="I1075" t="n">
+        <v>19797</v>
+      </c>
+      <c r="J1075" t="n">
+        <v>21457</v>
+      </c>
+      <c r="K1075" t="n">
+        <v>3322</v>
+      </c>
+      <c r="L1075" t="n">
+        <v>980</v>
+      </c>
+      <c r="M1075" t="n">
+        <v>2392</v>
+      </c>
+      <c r="N1075" t="n">
+        <v>355</v>
+      </c>
+      <c r="O1075" t="n">
+        <v>3605</v>
+      </c>
+      <c r="P1075" t="n">
+        <v>8548</v>
+      </c>
+      <c r="Q1075" t="n">
+        <v>14746</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58912,7 +58967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1074"/>
+  <dimension ref="A1:B1075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69657,6 +69712,16 @@
         <v>11741</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>11700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1075"/>
+  <dimension ref="A1:Q1076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58956,6 +58956,61 @@
         <v>14746</v>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>30193</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>3948</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>7929</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>11809</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>15028</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>17711</v>
+      </c>
+      <c r="I1076" t="n">
+        <v>19843</v>
+      </c>
+      <c r="J1076" t="n">
+        <v>21501</v>
+      </c>
+      <c r="K1076" t="n">
+        <v>3331</v>
+      </c>
+      <c r="L1076" t="n">
+        <v>983</v>
+      </c>
+      <c r="M1076" t="n">
+        <v>2403</v>
+      </c>
+      <c r="N1076" t="n">
+        <v>356</v>
+      </c>
+      <c r="O1076" t="n">
+        <v>3615</v>
+      </c>
+      <c r="P1076" t="n">
+        <v>8566</v>
+      </c>
+      <c r="Q1076" t="n">
+        <v>14779</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58967,7 +59022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1075"/>
+  <dimension ref="A1:B1076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69722,6 +69777,16 @@
         <v>11700</v>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>11700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1076"/>
+  <dimension ref="A1:Q1077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59011,6 +59011,61 @@
         <v>14779</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>30252</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>3951</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>7936</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>11822</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>15054</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>17749</v>
+      </c>
+      <c r="I1077" t="n">
+        <v>19888</v>
+      </c>
+      <c r="J1077" t="n">
+        <v>21550</v>
+      </c>
+      <c r="K1077" t="n">
+        <v>3339</v>
+      </c>
+      <c r="L1077" t="n">
+        <v>985</v>
+      </c>
+      <c r="M1077" t="n">
+        <v>2406</v>
+      </c>
+      <c r="N1077" t="n">
+        <v>355</v>
+      </c>
+      <c r="O1077" t="n">
+        <v>3627</v>
+      </c>
+      <c r="P1077" t="n">
+        <v>8586</v>
+      </c>
+      <c r="Q1077" t="n">
+        <v>14819</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59022,7 +59077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1076"/>
+  <dimension ref="A1:B1077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69787,6 +69842,16 @@
         <v>11700</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>11724</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1077"/>
+  <dimension ref="A1:Q1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59066,6 +59066,61 @@
         <v>14819</v>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>30254</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>3943</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>7932</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>11809</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>15038</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>17735</v>
+      </c>
+      <c r="I1078" t="n">
+        <v>19878</v>
+      </c>
+      <c r="J1078" t="n">
+        <v>21541</v>
+      </c>
+      <c r="K1078" t="n">
+        <v>3347</v>
+      </c>
+      <c r="L1078" t="n">
+        <v>989</v>
+      </c>
+      <c r="M1078" t="n">
+        <v>2403</v>
+      </c>
+      <c r="N1078" t="n">
+        <v>358</v>
+      </c>
+      <c r="O1078" t="n">
+        <v>3627</v>
+      </c>
+      <c r="P1078" t="n">
+        <v>8577</v>
+      </c>
+      <c r="Q1078" t="n">
+        <v>14806</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59077,7 +59132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1077"/>
+  <dimension ref="A1:B1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69852,6 +69907,16 @@
         <v>11724</v>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>11715</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1078"/>
+  <dimension ref="A1:Q1079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59121,6 +59121,61 @@
         <v>14806</v>
       </c>
     </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>30320</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>3949</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>7950</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>11830</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>15072</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>17777</v>
+      </c>
+      <c r="I1079" t="n">
+        <v>19936</v>
+      </c>
+      <c r="J1079" t="n">
+        <v>21603</v>
+      </c>
+      <c r="K1079" t="n">
+        <v>3354</v>
+      </c>
+      <c r="L1079" t="n">
+        <v>986</v>
+      </c>
+      <c r="M1079" t="n">
+        <v>2404</v>
+      </c>
+      <c r="N1079" t="n">
+        <v>356</v>
+      </c>
+      <c r="O1079" t="n">
+        <v>3649</v>
+      </c>
+      <c r="P1079" t="n">
+        <v>8615</v>
+      </c>
+      <c r="Q1079" t="n">
+        <v>14851</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59132,7 +59187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1078"/>
+  <dimension ref="A1:B1079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69917,6 +69972,16 @@
         <v>11715</v>
       </c>
     </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>11759</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1079"/>
+  <dimension ref="A1:Q1080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59176,6 +59176,61 @@
         <v>14851</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>30365</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>3955</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>7949</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>11836</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>15070</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>17787</v>
+      </c>
+      <c r="I1080" t="n">
+        <v>19957</v>
+      </c>
+      <c r="J1080" t="n">
+        <v>21625</v>
+      </c>
+      <c r="K1080" t="n">
+        <v>3367</v>
+      </c>
+      <c r="L1080" t="n">
+        <v>983</v>
+      </c>
+      <c r="M1080" t="n">
+        <v>2412</v>
+      </c>
+      <c r="N1080" t="n">
+        <v>358</v>
+      </c>
+      <c r="O1080" t="n">
+        <v>3656</v>
+      </c>
+      <c r="P1080" t="n">
+        <v>8617</v>
+      </c>
+      <c r="Q1080" t="n">
+        <v>14878</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59187,7 +59242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1079"/>
+  <dimension ref="A1:B1080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69982,6 +70037,16 @@
         <v>11759</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>11777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1080"/>
+  <dimension ref="A1:Q1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59231,6 +59231,61 @@
         <v>14878</v>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>30423</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>3961</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>7951</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>11830</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>15082</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>17807</v>
+      </c>
+      <c r="I1081" t="n">
+        <v>19975</v>
+      </c>
+      <c r="J1081" t="n">
+        <v>21660</v>
+      </c>
+      <c r="K1081" t="n">
+        <v>3382</v>
+      </c>
+      <c r="L1081" t="n">
+        <v>988</v>
+      </c>
+      <c r="M1081" t="n">
+        <v>2416</v>
+      </c>
+      <c r="N1081" t="n">
+        <v>359</v>
+      </c>
+      <c r="O1081" t="n">
+        <v>3655</v>
+      </c>
+      <c r="P1081" t="n">
+        <v>8625</v>
+      </c>
+      <c r="Q1081" t="n">
+        <v>14893</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59242,7 +59297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1080"/>
+  <dimension ref="A1:B1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70047,6 +70102,16 @@
         <v>11777</v>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>11778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1081"/>
+  <dimension ref="A1:Q1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59286,6 +59286,61 @@
         <v>14893</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>30522</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>7966</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>11862</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>15123</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>17857</v>
+      </c>
+      <c r="I1082" t="n">
+        <v>20029</v>
+      </c>
+      <c r="J1082" t="n">
+        <v>21724</v>
+      </c>
+      <c r="K1082" t="n">
+        <v>3396</v>
+      </c>
+      <c r="L1082" t="n">
+        <v>992</v>
+      </c>
+      <c r="M1082" t="n">
+        <v>2421</v>
+      </c>
+      <c r="N1082" t="n">
+        <v>360</v>
+      </c>
+      <c r="O1082" t="n">
+        <v>3662</v>
+      </c>
+      <c r="P1082" t="n">
+        <v>8644</v>
+      </c>
+      <c r="Q1082" t="n">
+        <v>14942</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59297,7 +59352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1081"/>
+  <dimension ref="A1:B1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70112,6 +70167,16 @@
         <v>11778</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>11803</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1082"/>
+  <dimension ref="A1:Q1083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59341,6 +59341,61 @@
         <v>14942</v>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>30584</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>3960</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>7971</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>11874</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>15141</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>17898</v>
+      </c>
+      <c r="I1083" t="n">
+        <v>20080</v>
+      </c>
+      <c r="J1083" t="n">
+        <v>21780</v>
+      </c>
+      <c r="K1083" t="n">
+        <v>3395</v>
+      </c>
+      <c r="L1083" t="n">
+        <v>997</v>
+      </c>
+      <c r="M1083" t="n">
+        <v>2419</v>
+      </c>
+      <c r="N1083" t="n">
+        <v>360</v>
+      </c>
+      <c r="O1083" t="n">
+        <v>3665</v>
+      </c>
+      <c r="P1083" t="n">
+        <v>8654</v>
+      </c>
+      <c r="Q1083" t="n">
+        <v>14974</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59352,7 +59407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1082"/>
+  <dimension ref="A1:B1083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70177,6 +70232,16 @@
         <v>11803</v>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>11787</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1083"/>
+  <dimension ref="A1:Q1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59396,6 +59396,61 @@
         <v>14974</v>
       </c>
     </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>30583</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>3960</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>7973</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>11881</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>15142</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>17901</v>
+      </c>
+      <c r="I1084" t="n">
+        <v>20085</v>
+      </c>
+      <c r="J1084" t="n">
+        <v>21778</v>
+      </c>
+      <c r="K1084" t="n">
+        <v>3384</v>
+      </c>
+      <c r="L1084" t="n">
+        <v>998</v>
+      </c>
+      <c r="M1084" t="n">
+        <v>2419</v>
+      </c>
+      <c r="N1084" t="n">
+        <v>359</v>
+      </c>
+      <c r="O1084" t="n">
+        <v>3663</v>
+      </c>
+      <c r="P1084" t="n">
+        <v>8658</v>
+      </c>
+      <c r="Q1084" t="n">
+        <v>14982</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59407,7 +59462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1083"/>
+  <dimension ref="A1:B1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70242,6 +70297,16 @@
         <v>11787</v>
       </c>
     </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>11738</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1084"/>
+  <dimension ref="A1:Q1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59451,6 +59451,61 @@
         <v>14982</v>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>30637</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>3970</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>7982</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>11901</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>15173</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>17938</v>
+      </c>
+      <c r="I1085" t="n">
+        <v>20132</v>
+      </c>
+      <c r="J1085" t="n">
+        <v>21817</v>
+      </c>
+      <c r="K1085" t="n">
+        <v>3388</v>
+      </c>
+      <c r="L1085" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M1085" t="n">
+        <v>2427</v>
+      </c>
+      <c r="N1085" t="n">
+        <v>360</v>
+      </c>
+      <c r="O1085" t="n">
+        <v>3666</v>
+      </c>
+      <c r="P1085" t="n">
+        <v>8673</v>
+      </c>
+      <c r="Q1085" t="n">
+        <v>15017</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59462,7 +59517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1084"/>
+  <dimension ref="A1:B1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70307,6 +70362,16 @@
         <v>11738</v>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>11703</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1085"/>
+  <dimension ref="A1:Q1086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59506,6 +59506,61 @@
         <v>15017</v>
       </c>
     </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>30700</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>3980</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>7995</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>11924</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>15209</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>17985</v>
+      </c>
+      <c r="I1086" t="n">
+        <v>20183</v>
+      </c>
+      <c r="J1086" t="n">
+        <v>21871</v>
+      </c>
+      <c r="K1086" t="n">
+        <v>3396</v>
+      </c>
+      <c r="L1086" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M1086" t="n">
+        <v>2430</v>
+      </c>
+      <c r="N1086" t="n">
+        <v>360</v>
+      </c>
+      <c r="O1086" t="n">
+        <v>3680</v>
+      </c>
+      <c r="P1086" t="n">
+        <v>8699</v>
+      </c>
+      <c r="Q1086" t="n">
+        <v>15058</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59517,7 +59572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1085"/>
+  <dimension ref="A1:B1086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70372,6 +70427,16 @@
         <v>11703</v>
       </c>
     </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>11711</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1086"/>
+  <dimension ref="A1:Q1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59561,6 +59561,61 @@
         <v>15058</v>
       </c>
     </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>30722</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>3985</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>8009</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>11933</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>15218</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>17988</v>
+      </c>
+      <c r="I1087" t="n">
+        <v>20193</v>
+      </c>
+      <c r="J1087" t="n">
+        <v>21879</v>
+      </c>
+      <c r="K1087" t="n">
+        <v>3402</v>
+      </c>
+      <c r="L1087" t="n">
+        <v>1017</v>
+      </c>
+      <c r="M1087" t="n">
+        <v>2433</v>
+      </c>
+      <c r="N1087" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1087" t="n">
+        <v>3694</v>
+      </c>
+      <c r="P1087" t="n">
+        <v>8720</v>
+      </c>
+      <c r="Q1087" t="n">
+        <v>15075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59572,7 +59627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1086"/>
+  <dimension ref="A1:B1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70437,6 +70492,16 @@
         <v>11711</v>
       </c>
     </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>11670</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1087"/>
+  <dimension ref="A1:Q1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59616,6 +59616,61 @@
         <v>15075</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>30739</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>8004</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>11928</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>15208</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>17983</v>
+      </c>
+      <c r="I1088" t="n">
+        <v>20194</v>
+      </c>
+      <c r="J1088" t="n">
+        <v>21881</v>
+      </c>
+      <c r="K1088" t="n">
+        <v>3412</v>
+      </c>
+      <c r="L1088" t="n">
+        <v>1015</v>
+      </c>
+      <c r="M1088" t="n">
+        <v>2434</v>
+      </c>
+      <c r="N1088" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1088" t="n">
+        <v>3694</v>
+      </c>
+      <c r="P1088" t="n">
+        <v>8715</v>
+      </c>
+      <c r="Q1088" t="n">
+        <v>15085</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59627,7 +59682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1087"/>
+  <dimension ref="A1:B1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70502,6 +70557,16 @@
         <v>11670</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>11616</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1088"/>
+  <dimension ref="A1:Q1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59671,6 +59671,61 @@
         <v>15085</v>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>30843</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>3999</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>8031</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>11964</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>15261</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>18045</v>
+      </c>
+      <c r="I1089" t="n">
+        <v>20265</v>
+      </c>
+      <c r="J1089" t="n">
+        <v>21958</v>
+      </c>
+      <c r="K1089" t="n">
+        <v>3425</v>
+      </c>
+      <c r="L1089" t="n">
+        <v>1015</v>
+      </c>
+      <c r="M1089" t="n">
+        <v>2448</v>
+      </c>
+      <c r="N1089" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1089" t="n">
+        <v>3698</v>
+      </c>
+      <c r="P1089" t="n">
+        <v>8743</v>
+      </c>
+      <c r="Q1089" t="n">
+        <v>15143</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59682,7 +59737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1088"/>
+  <dimension ref="A1:B1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70567,6 +70622,16 @@
         <v>11616</v>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>11635</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1089"/>
+  <dimension ref="A1:Q1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59726,6 +59726,61 @@
         <v>15143</v>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>30912</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>4002</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>8038</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>11981</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>15296</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>18084</v>
+      </c>
+      <c r="I1090" t="n">
+        <v>20312</v>
+      </c>
+      <c r="J1090" t="n">
+        <v>22011</v>
+      </c>
+      <c r="K1090" t="n">
+        <v>3429</v>
+      </c>
+      <c r="L1090" t="n">
+        <v>1020</v>
+      </c>
+      <c r="M1090" t="n">
+        <v>2454</v>
+      </c>
+      <c r="N1090" t="n">
+        <v>362</v>
+      </c>
+      <c r="O1090" t="n">
+        <v>3702</v>
+      </c>
+      <c r="P1090" t="n">
+        <v>8756</v>
+      </c>
+      <c r="Q1090" t="n">
+        <v>15173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59737,7 +59792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1089"/>
+  <dimension ref="A1:B1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70632,6 +70687,16 @@
         <v>11635</v>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>11617</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1090"/>
+  <dimension ref="A1:Q1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59781,6 +59781,61 @@
         <v>15173</v>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>30960</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>4008</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>8047</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>11991</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>15300</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>18089</v>
+      </c>
+      <c r="I1091" t="n">
+        <v>20327</v>
+      </c>
+      <c r="J1091" t="n">
+        <v>22036</v>
+      </c>
+      <c r="K1091" t="n">
+        <v>3430</v>
+      </c>
+      <c r="L1091" t="n">
+        <v>1016</v>
+      </c>
+      <c r="M1091" t="n">
+        <v>2469</v>
+      </c>
+      <c r="N1091" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1091" t="n">
+        <v>3697</v>
+      </c>
+      <c r="P1091" t="n">
+        <v>8772</v>
+      </c>
+      <c r="Q1091" t="n">
+        <v>15202</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59792,7 +59847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1090"/>
+  <dimension ref="A1:B1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70697,6 +70752,16 @@
         <v>11617</v>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>11607</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1091"/>
+  <dimension ref="A1:Q1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59836,6 +59836,61 @@
         <v>15202</v>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>31027</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>4008</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>8046</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>12003</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>15318</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>18120</v>
+      </c>
+      <c r="I1092" t="n">
+        <v>20368</v>
+      </c>
+      <c r="J1092" t="n">
+        <v>22078</v>
+      </c>
+      <c r="K1092" t="n">
+        <v>3434</v>
+      </c>
+      <c r="L1092" t="n">
+        <v>1016</v>
+      </c>
+      <c r="M1092" t="n">
+        <v>2479</v>
+      </c>
+      <c r="N1092" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1092" t="n">
+        <v>3707</v>
+      </c>
+      <c r="P1092" t="n">
+        <v>8785</v>
+      </c>
+      <c r="Q1092" t="n">
+        <v>15231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59847,7 +59902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1091"/>
+  <dimension ref="A1:B1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70762,6 +70817,16 @@
         <v>11607</v>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>11642</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1092"/>
+  <dimension ref="A1:Q1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59891,6 +59891,61 @@
         <v>15231</v>
       </c>
     </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>31056</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>4013</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>8053</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>12012</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>15335</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>18140</v>
+      </c>
+      <c r="I1093" t="n">
+        <v>20399</v>
+      </c>
+      <c r="J1093" t="n">
+        <v>22117</v>
+      </c>
+      <c r="K1093" t="n">
+        <v>3424</v>
+      </c>
+      <c r="L1093" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M1093" t="n">
+        <v>2480</v>
+      </c>
+      <c r="N1093" t="n">
+        <v>359</v>
+      </c>
+      <c r="O1093" t="n">
+        <v>3712</v>
+      </c>
+      <c r="P1093" t="n">
+        <v>8798</v>
+      </c>
+      <c r="Q1093" t="n">
+        <v>15253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59902,7 +59957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1092"/>
+  <dimension ref="A1:B1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70827,6 +70882,16 @@
         <v>11642</v>
       </c>
     </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>11616</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1093"/>
+  <dimension ref="A1:Q1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59946,6 +59946,61 @@
         <v>15253</v>
       </c>
     </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>31052</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>4007</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>8042</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>11999</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>15323</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>18129</v>
+      </c>
+      <c r="I1094" t="n">
+        <v>20387</v>
+      </c>
+      <c r="J1094" t="n">
+        <v>22113</v>
+      </c>
+      <c r="K1094" t="n">
+        <v>3426</v>
+      </c>
+      <c r="L1094" t="n">
+        <v>1015</v>
+      </c>
+      <c r="M1094" t="n">
+        <v>2478</v>
+      </c>
+      <c r="N1094" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1094" t="n">
+        <v>3714</v>
+      </c>
+      <c r="P1094" t="n">
+        <v>8792</v>
+      </c>
+      <c r="Q1094" t="n">
+        <v>15259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59957,7 +60012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1093"/>
+  <dimension ref="A1:B1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70892,6 +70947,16 @@
         <v>11616</v>
       </c>
     </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>11553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1094"/>
+  <dimension ref="A1:Q1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60001,6 +60001,61 @@
         <v>15259</v>
       </c>
     </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>31093</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>3995</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>8041</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>11998</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>15336</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>18143</v>
+      </c>
+      <c r="I1095" t="n">
+        <v>20404</v>
+      </c>
+      <c r="J1095" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K1095" t="n">
+        <v>3438</v>
+      </c>
+      <c r="L1095" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M1095" t="n">
+        <v>2476</v>
+      </c>
+      <c r="N1095" t="n">
+        <v>358</v>
+      </c>
+      <c r="O1095" t="n">
+        <v>3718</v>
+      </c>
+      <c r="P1095" t="n">
+        <v>8795</v>
+      </c>
+      <c r="Q1095" t="n">
+        <v>15272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -60012,7 +60067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1094"/>
+  <dimension ref="A1:B1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70957,6 +71012,16 @@
         <v>11553</v>
       </c>
     </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>11514</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1095"/>
+  <dimension ref="A1:Q1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60056,6 +60056,61 @@
         <v>15272</v>
       </c>
     </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>31181</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>3993</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>8051</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>12019</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>15370</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>18187</v>
+      </c>
+      <c r="I1096" t="n">
+        <v>20465</v>
+      </c>
+      <c r="J1096" t="n">
+        <v>22198</v>
+      </c>
+      <c r="K1096" t="n">
+        <v>3448</v>
+      </c>
+      <c r="L1096" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M1096" t="n">
+        <v>2487</v>
+      </c>
+      <c r="N1096" t="n">
+        <v>359</v>
+      </c>
+      <c r="O1096" t="n">
+        <v>3730</v>
+      </c>
+      <c r="P1096" t="n">
+        <v>8816</v>
+      </c>
+      <c r="Q1096" t="n">
+        <v>15316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -60067,7 +60122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1095"/>
+  <dimension ref="A1:B1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71022,6 +71077,16 @@
         <v>11514</v>
       </c>
     </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>11531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1096"/>
+  <dimension ref="A1:Q1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60111,6 +60111,61 @@
         <v>15316</v>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>31228</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>3995</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>8056</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>12033</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>15395</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>18211</v>
+      </c>
+      <c r="I1097" t="n">
+        <v>20497</v>
+      </c>
+      <c r="J1097" t="n">
+        <v>22238</v>
+      </c>
+      <c r="K1097" t="n">
+        <v>3450</v>
+      </c>
+      <c r="L1097" t="n">
+        <v>1014</v>
+      </c>
+      <c r="M1097" t="n">
+        <v>2488</v>
+      </c>
+      <c r="N1097" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1097" t="n">
+        <v>3742</v>
+      </c>
+      <c r="P1097" t="n">
+        <v>8845</v>
+      </c>
+      <c r="Q1097" t="n">
+        <v>15351</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -60122,7 +60177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1096"/>
+  <dimension ref="A1:B1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71087,6 +71142,16 @@
         <v>11531</v>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>11539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Centaline_sale_lease.xlsx
+++ b/Centaline_sale_lease.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1097"/>
+  <dimension ref="A1:Q1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60166,6 +60166,61 @@
         <v>15351</v>
       </c>
     </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>31275</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>3995</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>8065</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>12056</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>15422</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>18245</v>
+      </c>
+      <c r="I1098" t="n">
+        <v>20524</v>
+      </c>
+      <c r="J1098" t="n">
+        <v>22271</v>
+      </c>
+      <c r="K1098" t="n">
+        <v>3460</v>
+      </c>
+      <c r="L1098" t="n">
+        <v>1013</v>
+      </c>
+      <c r="M1098" t="n">
+        <v>2488</v>
+      </c>
+      <c r="N1098" t="n">
+        <v>361</v>
+      </c>
+      <c r="O1098" t="n">
+        <v>3746</v>
+      </c>
+      <c r="P1098" t="n">
+        <v>8864</v>
+      </c>
+      <c r="Q1098" t="n">
+        <v>15380</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -60177,7 +60232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1097"/>
+  <dimension ref="A1:B1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71152,6 +71207,16 @@
         <v>11539</v>
       </c>
     </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>11561</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
